--- a/src/attributions/attributions_saliency_traj_407.xlsx
+++ b/src/attributions/attributions_saliency_traj_407.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG10"/>
+  <dimension ref="A1:GG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02525671571493149</v>
+        <v>0.1995804309844971</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3057905733585358</v>
+        <v>1.350084066390991</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03118367865681648</v>
+        <v>0.3228892087936401</v>
       </c>
       <c r="D2" t="n">
-        <v>0.20915886759758</v>
+        <v>0.7935881614685059</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006038784980773926</v>
+        <v>0.02332455292344093</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07093846052885056</v>
+        <v>0.5060102939605713</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01482649520039558</v>
+        <v>0.3843849301338196</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0180016178637743</v>
+        <v>0.07721985876560211</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04271698370575905</v>
+        <v>0.2517905235290527</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03606494516134262</v>
+        <v>0.01999975740909576</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2342743128538132</v>
+        <v>1.501859784126282</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01292692217975855</v>
+        <v>0.3065541982650757</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1942909806966782</v>
+        <v>1.05989944934845</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01216321624815464</v>
+        <v>0.1004008203744888</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04789460450410843</v>
+        <v>0.3245802819728851</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02058569341897964</v>
+        <v>0.3114675581455231</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04162141680717468</v>
+        <v>0.2374944686889648</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05077425017952919</v>
+        <v>0.09093333035707474</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02476776763796806</v>
+        <v>0.01992827095091343</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03934841230511665</v>
+        <v>0.2318502366542816</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004087402485311031</v>
+        <v>0.1434449851512909</v>
       </c>
       <c r="V2" t="n">
-        <v>0.03379236906766891</v>
+        <v>0.06160209327936172</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01767688803374767</v>
+        <v>0.02561376057565212</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01487808674573898</v>
+        <v>0.4116405248641968</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01290125213563442</v>
+        <v>0.01136197336018085</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.04093416407704353</v>
+        <v>0.05511374771595001</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.02489522844552994</v>
+        <v>0.2008223533630371</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.03662816435098648</v>
+        <v>0.1398696750402451</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.03551101684570312</v>
+        <v>0.2021463960409164</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.03753918409347534</v>
+        <v>0.07853193581104279</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.04862003028392792</v>
+        <v>0.475530594587326</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.00781997200101614</v>
+        <v>0.3054056465625763</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.001176564022898674</v>
+        <v>0.1469874680042267</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.001310250838287175</v>
+        <v>0.1559237092733383</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.001137940213084221</v>
+        <v>0.008342038840055466</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.02066989615559578</v>
+        <v>0.05377668514847755</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.00701890466734767</v>
+        <v>0.01608525775372982</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.03631986677646637</v>
+        <v>0.3220973610877991</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.007257694378495216</v>
+        <v>0.1351827681064606</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.005506574176251888</v>
+        <v>0.1268888115882874</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.001214023097418249</v>
+        <v>0.4569587409496307</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.04454809054732323</v>
+        <v>0.2736920714378357</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.001209230162203312</v>
+        <v>0.1209545284509659</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.02092359587550163</v>
+        <v>0.03239042684435844</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.03061426617205143</v>
+        <v>0.03532519936561584</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.03445687890052795</v>
+        <v>0.068622887134552</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.1363499313592911</v>
+        <v>0.7826622724533081</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.03614398464560509</v>
+        <v>0.1026612147688866</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.06056914478540421</v>
+        <v>0.5545778274536133</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.02770985290408134</v>
+        <v>0.1663365066051483</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.06928833574056625</v>
+        <v>0.08665031939744949</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.01651714369654655</v>
+        <v>0.0230963509529829</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.003688162192702293</v>
+        <v>0.01351703144609928</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.06614922732114792</v>
+        <v>0.03002286702394485</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.01445811428129673</v>
+        <v>0.3570679724216461</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.08259683102369308</v>
+        <v>0.005661562085151672</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.05971038341522217</v>
+        <v>0.3258395791053772</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.06907114386558533</v>
+        <v>0.05092176795005798</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.03042140603065491</v>
+        <v>0.02127000689506531</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.0004756519047077745</v>
+        <v>0.2626894116401672</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.02292391657829285</v>
+        <v>0.06829299032688141</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.03973215818405151</v>
+        <v>0.1080464869737625</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.003606543410569429</v>
+        <v>0.3016091287136078</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.01616103388369083</v>
+        <v>0.0001696944236755371</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.008475165814161301</v>
+        <v>0.3430517613887787</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.02823065221309662</v>
+        <v>0.00761185958981514</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.01978664472699165</v>
+        <v>0.1128700226545334</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.009705984033644199</v>
+        <v>0.01243128906935453</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.007621523458510637</v>
+        <v>0.007481895387172699</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.01240385323762894</v>
+        <v>0.150038093328476</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.01522925216704607</v>
+        <v>0.08735156059265137</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.008751558139920235</v>
+        <v>0.04983728751540184</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.04514497518539429</v>
+        <v>0.04268680512905121</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.0853833481669426</v>
+        <v>0.7204408645629883</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.02603939548134804</v>
+        <v>0.01484927255660295</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.05195251479744911</v>
+        <v>0.4204393923282623</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.000464485608972609</v>
+        <v>0.04352813959121704</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.002474699169397354</v>
+        <v>0.3631928563117981</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.001001858152449131</v>
+        <v>0.004405256360769272</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.02662379294633865</v>
+        <v>0.04303114116191864</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.05399547889828682</v>
+        <v>0.2498792707920074</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.007361195515841246</v>
+        <v>0.0476033054292202</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.0462510958313942</v>
+        <v>0.4212327599525452</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.02358756959438324</v>
+        <v>0.1844161003828049</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.03694109618663788</v>
+        <v>0.2826502621173859</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01070003490895033</v>
+        <v>0.06858615577220917</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.003297209972515702</v>
+        <v>0.03549901768565178</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.01675610616803169</v>
+        <v>0.03427309915423393</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.0001630028709769249</v>
+        <v>0.0948595255613327</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.01119724847376347</v>
+        <v>0.1003679484128952</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.0214322954416275</v>
+        <v>0.05224162340164185</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.009822678752243519</v>
+        <v>0.2744860947132111</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0222790539264679</v>
+        <v>0.3068536818027496</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.007588602602481842</v>
+        <v>0.5428579449653625</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.002518211724236608</v>
+        <v>0.04262854531407356</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.03354571759700775</v>
+        <v>0.03331737965345383</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.03480769693851471</v>
+        <v>0.1597659587860107</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.05553889647126198</v>
+        <v>0.05187824368476868</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.006108356639742851</v>
+        <v>0.2233216464519501</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.003666700562462211</v>
+        <v>0.02143964171409607</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.05104656890034676</v>
+        <v>0.427192896604538</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.02995595335960388</v>
+        <v>0.1669455617666245</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.04314450547099113</v>
+        <v>0.3080864548683167</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.0107633899897337</v>
+        <v>0.02682660333812237</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.001367162331007421</v>
+        <v>0.01927626505494118</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.01792280375957489</v>
+        <v>0.05764563009142876</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.01085163559764624</v>
+        <v>0.08746673911809921</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.004861184395849705</v>
+        <v>0.1135098040103912</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.01354443188756704</v>
+        <v>0.1615159064531326</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.1260483413934708</v>
+        <v>0.5510551929473877</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.01489324402064085</v>
+        <v>0.1512178927659988</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.1205721348524094</v>
+        <v>0.2626040875911713</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.005355739500373602</v>
+        <v>0.04098061844706535</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.02717752754688263</v>
+        <v>0.09325896948575974</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.0248853899538517</v>
+        <v>0.02721080556511879</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.02379694208502769</v>
+        <v>0.4798861742019653</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.003940485417842865</v>
+        <v>0.0839228555560112</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.01422508247196674</v>
+        <v>0.008194366469979286</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.02702413126826286</v>
+        <v>0.1044472306966782</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.007076963782310486</v>
+        <v>0.05711100995540619</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.02957305125892162</v>
+        <v>0.1558298170566559</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.03310137614607811</v>
+        <v>0.1327200084924698</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.02972161769866943</v>
+        <v>0.05527440458536148</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.01433215383440256</v>
+        <v>0.08959752321243286</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.009767681360244751</v>
+        <v>0.1233536973595619</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.03224871680140495</v>
+        <v>0.3790683150291443</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.00394620792940259</v>
+        <v>0.1318207830190659</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.03734543547034264</v>
+        <v>0.1941048502922058</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.01414686068892479</v>
+        <v>0.1708914041519165</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.03691274300217628</v>
+        <v>0.06620277464389801</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.01602735556662083</v>
+        <v>0.09937964379787445</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.02803500182926655</v>
+        <v>0.06916264444589615</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.01127615571022034</v>
+        <v>0.00878635048866272</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.01497232168912888</v>
+        <v>0.3841721415519714</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.004653594922274351</v>
+        <v>0.2788983285427094</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.001934215659275651</v>
+        <v>0.1014716774225235</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.03113478422164917</v>
+        <v>0.4135252237319946</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.02684664167463779</v>
+        <v>0.08600278198719025</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.006524722557514906</v>
+        <v>0.2494400292634964</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.0261426717042923</v>
+        <v>0.0201789028942585</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.005817596334964037</v>
+        <v>0.07629909366369247</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.002769959159195423</v>
+        <v>0.05348112434148788</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.009653367102146149</v>
+        <v>0.06009658053517342</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.002773966640233994</v>
+        <v>0.09659041464328766</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.002328015398234129</v>
+        <v>0.08945491909980774</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.01544294320046902</v>
+        <v>0.3038233816623688</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.03975814953446388</v>
+        <v>0.1308638006448746</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.03259808197617531</v>
+        <v>0.1772750467061996</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.01132812444120646</v>
+        <v>0.07966391742229462</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.05780117958784103</v>
+        <v>0.01759030669927597</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.03344286978244781</v>
+        <v>0.1613956987857819</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.0005563083104789257</v>
+        <v>0.1349357515573502</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.01486638002097607</v>
+        <v>0.2135470062494278</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.00196507666260004</v>
+        <v>0.04518517106771469</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.04777132719755173</v>
+        <v>0.4446538090705872</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.02532540261745453</v>
+        <v>0.1576794534921646</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.04079544916749001</v>
+        <v>0.3469637036323547</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.01298094261437654</v>
+        <v>0.08451561629772186</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.002210918115451932</v>
+        <v>0.0195142924785614</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.02767235785722733</v>
+        <v>0.06034765392541885</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.01119020581245422</v>
+        <v>0.1289689540863037</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.01275845989584923</v>
+        <v>0.09853947907686234</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.01266332156956196</v>
+        <v>0.06369412690401077</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.01595821604132652</v>
+        <v>0.2300271093845367</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.008584605529904366</v>
+        <v>0.1307598352432251</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.005401907488703728</v>
+        <v>0.2010289132595062</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.02132865786552429</v>
+        <v>0.1217385232448578</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.006303821224719286</v>
+        <v>0.09700756520032883</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.01119671016931534</v>
+        <v>0.04322110861539841</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.003547368105500937</v>
+        <v>0.01425750460475683</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.03132900968194008</v>
+        <v>0.2724753320217133</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.00746630784124136</v>
+        <v>0.1790323406457901</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.02017194777727127</v>
+        <v>0.3212952315807343</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.05150183290243149</v>
+        <v>0.4719160795211792</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.002788781421259046</v>
+        <v>0.5299603939056396</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.02602851204574108</v>
+        <v>0.4981335997581482</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.0178700964897871</v>
+        <v>0.06413102149963379</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.0001262491568922997</v>
+        <v>0.03950589522719383</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.02445056289434433</v>
+        <v>0.02468125149607658</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.01016621757298708</v>
+        <v>0.2117595672607422</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.02519284188747406</v>
+        <v>0.3010750114917755</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.004548451863229275</v>
+        <v>0.3936994075775146</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.002119178418070078</v>
+        <v>0.3468154966831207</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.008503132499754429</v>
+        <v>0.2835931181907654</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.07728421688079834</v>
+        <v>0.2240851074457169</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.03271722048521042</v>
+        <v>0.1222974061965942</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.08264575898647308</v>
+        <v>0.2942787110805511</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.01053020171821117</v>
+        <v>0.2147127538919449</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.003000307828187943</v>
+        <v>0.04968316853046417</v>
       </c>
     </row>
     <row r="3">
@@ -2137,1709 +2137,1709 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.4709700644016266</v>
+        <v>0.00434960937127471</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2016991376876831</v>
+        <v>0.0007156087085604668</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03202271834015846</v>
+        <v>0.001292939181439579</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00597434863448143</v>
+        <v>0.0001751299860188738</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07932505011558533</v>
+        <v>0.001286258222535253</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06245521456003189</v>
+        <v>0.00104961555916816</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09948410093784332</v>
+        <v>0.0008237092988565564</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01684994623064995</v>
+        <v>0.001437834464013577</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05284624919295311</v>
+        <v>0.0001340957824140787</v>
       </c>
       <c r="J4" t="n">
-        <v>0.434141218662262</v>
+        <v>0.004513941705226898</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01855713129043579</v>
+        <v>0.001577812945470214</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07451280951499939</v>
+        <v>0.001085960422642529</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07276269048452377</v>
+        <v>0.001577334362082183</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2323605120182037</v>
+        <v>0.001756123499944806</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2020816653966904</v>
+        <v>0.0004073545860592276</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1809896528720856</v>
+        <v>0.001252414542250335</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.07816124707460403</v>
+        <v>0.001064048614352942</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1404718905687332</v>
+        <v>0.0006610901327803731</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05190399661660194</v>
+        <v>0.0001596409128978848</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01979807391762733</v>
+        <v>0.0003589876287151128</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05428474768996239</v>
+        <v>0.0005663203774020076</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001351107843220234</v>
+        <v>0.0003229893336538225</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2440003454685211</v>
+        <v>0.0003413291997276247</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002008885145187378</v>
+        <v>0.0002434445486869663</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1383571922779083</v>
+        <v>0.0004222194838803262</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1016595065593719</v>
+        <v>5.26467920280993e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.07024931907653809</v>
+        <v>0.0001154532801592723</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02701808325946331</v>
+        <v>0.0008515414083376527</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.02405473589897156</v>
+        <v>5.747170143877156e-05</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.04156529903411865</v>
+        <v>0.0001727709022816271</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.03924600034952164</v>
+        <v>0.00169712130445987</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1953378170728683</v>
+        <v>0.0005035604699514806</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.05520999431610107</v>
+        <v>0.001023739809170365</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.07290668040513992</v>
+        <v>0.0006258883513510227</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.1386238485574722</v>
+        <v>0.001080559915862978</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.06087109446525574</v>
+        <v>0.0001882971992017701</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.1233249604701996</v>
+        <v>0.0003559248289093375</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.04770052433013916</v>
+        <v>0.001455652294680476</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0452154204249382</v>
+        <v>0.0003600366471800953</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.09822052717208862</v>
+        <v>0.0003652070299722254</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.1671804785728455</v>
+        <v>0.0002736136084422469</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.05117025971412659</v>
+        <v>0.0004707512562163174</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.06870473176240921</v>
+        <v>0.0003310817410238087</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.02752308547496796</v>
+        <v>0.0001890032435767353</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.01761353015899658</v>
+        <v>0.0002918058889918029</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.2790559828281403</v>
+        <v>0.003091863822191954</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1087625175714493</v>
+        <v>0.001266072387807071</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.03428378328680992</v>
+        <v>0.001172824297100306</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1049751788377762</v>
+        <v>0.0008208844810724258</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.002321689389646053</v>
+        <v>0.001022234326228499</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.07108242064714432</v>
+        <v>0.0007546014385297894</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1406052857637405</v>
+        <v>0.0003902214230038226</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.03519272804260254</v>
+        <v>0.00103740906342864</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0220874547958374</v>
+        <v>1.096021151170135e-05</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.09293414652347565</v>
+        <v>0.000456840090919286</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.2132397294044495</v>
+        <v>0.0001366005890304223</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.04188984259963036</v>
+        <v>3.177776306984015e-05</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.2203936129808426</v>
+        <v>0.0002586655900813639</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.07902456820011139</v>
+        <v>0.001733715063892305</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.05985074490308762</v>
+        <v>0.0006569824763573706</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.1321475058794022</v>
+        <v>0.0004366333014331758</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.2094674110412598</v>
+        <v>0.0002734873560257256</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.06151062995195389</v>
+        <v>0.0004127248539589345</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.04241172224283218</v>
+        <v>0.001173679367639124</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.157427966594696</v>
+        <v>2.011314063565806e-05</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.09105382859706879</v>
+        <v>0.0003827706095762551</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.04183560609817505</v>
+        <v>0.001557089504785836</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.1557870656251907</v>
+        <v>0.0008112950017675757</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.1857731342315674</v>
+        <v>0.0001152464392362162</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.01157956290990114</v>
+        <v>6.703313556499779e-05</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.06182169169187546</v>
+        <v>0.0003394470550119877</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0278558861464262</v>
+        <v>0.0001029557242873125</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.1779080927371979</v>
+        <v>0.001198594574816525</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.02914532832801342</v>
+        <v>0.0003297769580967724</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.02030432969331741</v>
+        <v>0.001322944764979184</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.1447626799345016</v>
+        <v>0.0005252841510809958</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.1467798203229904</v>
+        <v>0.0003914829576388001</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.03617433831095695</v>
+        <v>5.741007043980062e-06</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.02947024255990982</v>
+        <v>0.0001117427018471062</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.008124749176204205</v>
+        <v>0.0004363940097391605</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.04016617685556412</v>
+        <v>0.0007422647322528064</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.09110406041145325</v>
+        <v>0.001019946066662669</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.09211382269859314</v>
+        <v>0.0004558352520689368</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003257917705923319</v>
+        <v>0.000118558484246023</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.06580334901809692</v>
+        <v>0.0004966739215888083</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.006697865668684244</v>
+        <v>0.000113580230390653</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.04756949096918106</v>
+        <v>9.015452087623999e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.01453998684883118</v>
+        <v>0.0004869972181040794</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.1046220287680626</v>
+        <v>2.184876393585e-05</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.001548677682876587</v>
+        <v>2.783180025289766e-05</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.05705839022994041</v>
+        <v>0.0003805534215644002</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.009606471285223961</v>
+        <v>0.00136589864268899</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.09404442459344864</v>
+        <v>0.0005253033596090972</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.006394602358341217</v>
+        <v>0.001159874023869634</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.1420347988605499</v>
+        <v>0.0002310242271050811</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.1639234572649002</v>
+        <v>0.0006545729120261967</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.03760125488042831</v>
+        <v>0.001350043108686805</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.06936116516590118</v>
+        <v>0.001929715275764465</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.007526887580752373</v>
+        <v>1.603165583219379e-05</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.08566788583993912</v>
+        <v>0.0009429467609152198</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.09317930787801743</v>
+        <v>0.0007985198171809316</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.005090073682367802</v>
+        <v>0.0002284746442455798</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.02494385838508606</v>
+        <v>0.0005179938161745667</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.01116307452321053</v>
+        <v>0.0002068683097604662</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.01441565249115229</v>
+        <v>0.0001726488408166915</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.00460260733962059</v>
+        <v>0.0002925883163698018</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.1023150458931923</v>
+        <v>0.0001440363703295588</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.02206237614154816</v>
+        <v>0.0001195175791508518</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1015605106949806</v>
+        <v>0.0006493982509709895</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.02911977469921112</v>
+        <v>0.003042500698938966</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0119766928255558</v>
+        <v>0.0003168715920764953</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.2723936140537262</v>
+        <v>0.0008283063070848584</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.04372838884592056</v>
+        <v>0.001285938895307481</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.1760881841182709</v>
+        <v>0.0005174994585104287</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.08871746808290482</v>
+        <v>0.0004989188746549189</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.1624301075935364</v>
+        <v>0.0002684782084543258</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0004391474649310112</v>
+        <v>0.0007640974363312125</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.06786587834358215</v>
+        <v>0.001163212698884308</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.007518717553466558</v>
+        <v>0.0006287401192821562</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.02282924577593803</v>
+        <v>0.0003143659268971533</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.05375398695468903</v>
+        <v>4.193202767055482e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.03607792034745216</v>
+        <v>0.0008351907599717379</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.04758702218532562</v>
+        <v>0.0002246915246360004</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.1212070882320404</v>
+        <v>0.0003052147221751511</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.1628439277410507</v>
+        <v>0.0004619786341208965</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.04635782912373543</v>
+        <v>5.963705916656181e-05</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.04633720964193344</v>
+        <v>0.0004362639156170189</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.1447810083627701</v>
+        <v>0.0001332585234194994</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.02376296557486057</v>
+        <v>0.000988540006801486</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.05801358446478844</v>
+        <v>0.0006570839323103428</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.130903959274292</v>
+        <v>0.0009034852264449</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.04646004363894463</v>
+        <v>0.0001747336646076292</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.003224269486963749</v>
+        <v>9.231232252204791e-05</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.1563073545694351</v>
+        <v>7.083325181156397e-05</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0282893069088459</v>
+        <v>7.62777854106389e-05</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.08721115440130234</v>
+        <v>0.0007551249000243843</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.09019505232572556</v>
+        <v>0.0003089802339673042</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.02040327526628971</v>
+        <v>6.912447133800015e-05</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.03490646183490753</v>
+        <v>0.0008759355405345559</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.04341801628470421</v>
+        <v>0.0001729071082081646</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.003962857648730278</v>
+        <v>3.93329537473619e-06</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.005375485867261887</v>
+        <v>0.0006338571547530591</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.03854865580797195</v>
+        <v>0.0001497800694778562</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.009114492684602737</v>
+        <v>0.0004432962159626186</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.1143855899572372</v>
+        <v>0.0005890080356039107</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.06076596304774284</v>
+        <v>0.001479163882322609</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.04363085329532623</v>
+        <v>0.0002527513715904206</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.004344120621681213</v>
+        <v>0.0006413217051886022</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.08840898424386978</v>
+        <v>0.0001844709913711995</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0135217010974884</v>
+        <v>0.0005209489027038217</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.09574328362941742</v>
+        <v>0.0002998411655426025</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.106278270483017</v>
+        <v>0.0001384244242217392</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.06740310788154602</v>
+        <v>0.0007014486473053694</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.1027709394693375</v>
+        <v>0.0008948528557084501</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0556568019092083</v>
+        <v>0.000827015726827085</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.005483398679643869</v>
+        <v>0.0003645441902335733</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.04416259005665779</v>
+        <v>0.0001545319973956794</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.01228119339793921</v>
+        <v>3.703817492350936e-05</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.04277031123638153</v>
+        <v>0.0003401118447072804</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.01632390357553959</v>
+        <v>0.0004858379543293267</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.1027798503637314</v>
+        <v>0.0001262197038158774</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.02169610373675823</v>
+        <v>0.0001077939377864823</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.1051431149244308</v>
+        <v>0.002257896820083261</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.08369869738817215</v>
+        <v>2.807972487062216e-05</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.09431827068328857</v>
+        <v>0.0001097471104003489</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.005860641598701477</v>
+        <v>0.001417475170455873</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.08313753455877304</v>
+        <v>0.0002348943235119805</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.02625519409775734</v>
+        <v>0.0001904872915474698</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.03210621327161789</v>
+        <v>0.000318006903398782</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.02480577677488327</v>
+        <v>0.0005107379984110594</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.009348150342702866</v>
+        <v>3.280662349425256e-05</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.2256025671958923</v>
+        <v>0.0005630821688100696</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.05891487002372742</v>
+        <v>0.002111442387104034</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.0001479904167354107</v>
+        <v>0.00120723934378475</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.119221068918705</v>
+        <v>0.002158857649192214</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.2285601198673248</v>
+        <v>0.001020399853587151</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.05755100026726723</v>
+        <v>0.001020332332700491</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.1113178431987762</v>
+        <v>0.0004595243080984801</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.02468210458755493</v>
+        <v>0.0004331863601692021</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.01982459798455238</v>
+        <v>0.0004540783993434161</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.0309160053730011</v>
+        <v>0.001326346886344254</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.00488705188035965</v>
+        <v>0.001374299172312021</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.1309687346220016</v>
+        <v>0.0001000658303382806</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.05401292815804482</v>
+        <v>0.001035738503560424</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.1879600137472153</v>
+        <v>0.00137395563069731</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.07399698346853256</v>
+        <v>0.0004366695939097553</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.003435853868722916</v>
+        <v>0.0005125475581735373</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.09873493015766144</v>
+        <v>0.001535613206215203</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.1261413544416428</v>
+        <v>5.601448356173933e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.1569704860448837</v>
+        <v>0.04965219274163246</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8717491030693054</v>
+        <v>0.4384437501430511</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1020403504371643</v>
+        <v>0.0223701000213623</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3895395696163177</v>
+        <v>0.7618063688278198</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2346254885196686</v>
+        <v>0.04510262981057167</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3080594837665558</v>
+        <v>0.1047209948301315</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1124903485178947</v>
+        <v>0.119204469025135</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06213546544313431</v>
+        <v>0.1557577252388</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02638521604239941</v>
+        <v>0.01841355673968792</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1515984833240509</v>
+        <v>0.1569169163703918</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6188448667526245</v>
+        <v>0.3324015736579895</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02650029398500919</v>
+        <v>0.0950762927532196</v>
       </c>
       <c r="M5" t="n">
-        <v>0.301543653011322</v>
+        <v>0.9614095687866211</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3195295333862305</v>
+        <v>0.0059090880677104</v>
       </c>
       <c r="O5" t="n">
-        <v>0.344221830368042</v>
+        <v>0.06627101451158524</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1598226875066757</v>
+        <v>0.226137787103653</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1319735944271088</v>
+        <v>0.05459491163492203</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1118620783090591</v>
+        <v>0.05185459554195404</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02380799874663353</v>
+        <v>0.0183374434709549</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1034996956586838</v>
+        <v>0.04651622474193573</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01725424826145172</v>
+        <v>0.07583990693092346</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1047713905572891</v>
+        <v>0.01144618541002274</v>
       </c>
       <c r="W5" t="n">
-        <v>0.08518870919942856</v>
+        <v>0.08401778340339661</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1302136927843094</v>
+        <v>0.09436000883579254</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.138397753238678</v>
+        <v>0.0313786007463932</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.07026781886816025</v>
+        <v>0.1481725722551346</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.08340154588222504</v>
+        <v>0.01389903761446476</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.01363168656826019</v>
+        <v>0.00232706218957901</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1022683531045914</v>
+        <v>0.04447529092431068</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.01540394965559244</v>
+        <v>0.05476634949445724</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.02492907084524632</v>
+        <v>0.02383164130151272</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.07069890946149826</v>
+        <v>0.0830560177564621</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.05604390054941177</v>
+        <v>0.002996081486344337</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.07779914140701294</v>
+        <v>0.08776853233575821</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.01917487382888794</v>
+        <v>0.05511818826198578</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.07079008221626282</v>
+        <v>0.1766444593667984</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.06983849406242371</v>
+        <v>0.00456557422876358</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.1646854132413864</v>
+        <v>0.1554818451404572</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.06525734066963196</v>
+        <v>0.03064447827637196</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.04225511476397514</v>
+        <v>0.1586352735757828</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.06142458692193031</v>
+        <v>0.1544589698314667</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.1266049742698669</v>
+        <v>0.1242040544748306</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.04180967807769775</v>
+        <v>0.0721137747168541</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0225818008184433</v>
+        <v>0.1160819381475449</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.09120577573776245</v>
+        <v>0.001547666266560555</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.08232375234365463</v>
+        <v>0.005340208299458027</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.5760775208473206</v>
+        <v>0.2709676623344421</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.08636416494846344</v>
+        <v>0.02357449755072594</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1751153916120529</v>
+        <v>0.4531535506248474</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.09445145726203918</v>
+        <v>0.3069936633110046</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.1041301414370537</v>
+        <v>0.0312519371509552</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.02845323830842972</v>
+        <v>0.01550509035587311</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.06353664398193359</v>
+        <v>0.02840202674269676</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.1277446299791336</v>
+        <v>0.1900694668292999</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.08741531521081924</v>
+        <v>0.005985310301184654</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1287501156330109</v>
+        <v>0.04488299414515495</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.111552506685257</v>
+        <v>0.04366620630025864</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.01712564937770367</v>
+        <v>0.01301837339997292</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.1874420344829559</v>
+        <v>0.02570853382349014</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.1341578662395477</v>
+        <v>0.1257002204656601</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.09765317291021347</v>
+        <v>0.04581015929579735</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.01777536794543266</v>
+        <v>0.03828039020299911</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.03935350105166435</v>
+        <v>0.2368529438972473</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.09471018612384796</v>
+        <v>0.04762433469295502</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03258252516388893</v>
+        <v>0.08271694928407669</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0276958029717207</v>
+        <v>0.05871337652206421</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.09325698018074036</v>
+        <v>0.02139034867286682</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01657197624444962</v>
+        <v>0.1179047003388405</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.003158915787935257</v>
+        <v>0.09895727038383484</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.02473398111760616</v>
+        <v>0.0002573054516687989</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0547151044011116</v>
+        <v>0.04684341698884964</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.05320513993501663</v>
+        <v>0.03306952118873596</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.07035566866397858</v>
+        <v>0.007814912125468254</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.3227510452270508</v>
+        <v>0.2479049265384674</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.04495994001626968</v>
+        <v>0.01557414047420025</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.1436659693717957</v>
+        <v>0.3328052163124084</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.1540645360946655</v>
+        <v>0.05219031125307083</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.1419061273336411</v>
+        <v>0.0662141740322113</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.05055313929915428</v>
+        <v>0.05074203014373779</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.07707223296165466</v>
+        <v>0.06974441558122635</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.06787113845348358</v>
+        <v>0.02111718989908695</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.06855668872594833</v>
+        <v>0.04521721601486206</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1268159598112106</v>
+        <v>0.1520200371742249</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.05177851393818855</v>
+        <v>0.0220852792263031</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.03347623348236084</v>
+        <v>0.276894211769104</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01763969659805298</v>
+        <v>0.04954641312360764</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0821554958820343</v>
+        <v>0.01940356567502022</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.01619491912424564</v>
+        <v>0.007549978792667389</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.02265461906790733</v>
+        <v>0.08385732024908066</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.05393918976187706</v>
+        <v>0.01914777792990208</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.06546429544687271</v>
+        <v>0.02033868432044983</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.03826242685317993</v>
+        <v>0.1152378767728806</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.04055286198854446</v>
+        <v>0.06340380012989044</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.08585294336080551</v>
+        <v>0.4391047358512878</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.11771509796381</v>
+        <v>0.08913777768611908</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0250478982925415</v>
+        <v>0.03230966627597809</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.1131891310214996</v>
+        <v>0.04409581050276756</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.1289375871419907</v>
+        <v>0.02699708938598633</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.002578253857791424</v>
+        <v>0.04063045606017113</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.05549636483192444</v>
+        <v>0.04919721186161041</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.1172451376914978</v>
+        <v>0.1475298404693604</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0383625291287899</v>
+        <v>0.03852222859859467</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.07221308350563049</v>
+        <v>0.2816030383110046</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.02764089591801167</v>
+        <v>0.03018895164132118</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.1204183548688889</v>
+        <v>0.02389197610318661</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.01084907725453377</v>
+        <v>0.03278578072786331</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.02869170904159546</v>
+        <v>0.0730876624584198</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.02518289722502232</v>
+        <v>0.0143933966755867</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.05156632512807846</v>
+        <v>0.03613192588090897</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.1064116507768631</v>
+        <v>0.2075072228908539</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.01783940009772778</v>
+        <v>0.1022248715162277</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.05485083907842636</v>
+        <v>0.1556024253368378</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1256690323352814</v>
+        <v>0.1985645890235901</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.00454508513212204</v>
+        <v>0.09570096433162689</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0491492748260498</v>
+        <v>0.008612751960754395</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.06392652541399002</v>
+        <v>0.2677153050899506</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.05007191002368927</v>
+        <v>0.1112155467271805</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.1214304566383362</v>
+        <v>0.02239229716360569</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.09725242853164673</v>
+        <v>0.04744531959295273</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0284875426441431</v>
+        <v>0.03167868033051491</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.06410981714725494</v>
+        <v>0.1525129526853561</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.007262926548719406</v>
+        <v>0.03155349940061569</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.09098457545042038</v>
+        <v>0.04032113403081894</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.005204042419791222</v>
+        <v>0.101647213101387</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.04740612208843231</v>
+        <v>0.07286084443330765</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.09462130814790726</v>
+        <v>0.266635537147522</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.04194024205207825</v>
+        <v>0.01950029470026493</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.02543787285685539</v>
+        <v>0.02400887385010719</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.1674106419086456</v>
+        <v>0.1039576977491379</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.02614318206906319</v>
+        <v>0.1517297178506851</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.01151648536324501</v>
+        <v>0.1198639571666718</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.06331392377614975</v>
+        <v>0.008462809026241302</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.03525810688734055</v>
+        <v>0.04044497758150101</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.05633174628019333</v>
+        <v>0.2929912507534027</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.03080183826386929</v>
+        <v>0.2336180806159973</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0305244717746973</v>
+        <v>0.1712253987789154</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.01429415494203568</v>
+        <v>0.1277153640985489</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.02345776185393333</v>
+        <v>0.05265451595187187</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.03563233464956284</v>
+        <v>0.2007891833782196</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.01421842910349369</v>
+        <v>0.03859009966254234</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.1131518483161926</v>
+        <v>0.01643602922558784</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.03839836269617081</v>
+        <v>0.02314771339297295</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.03121811710298061</v>
+        <v>0.002155105583369732</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.003888309001922607</v>
+        <v>0.04810214042663574</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.02423407137393951</v>
+        <v>0.0692814439535141</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.074107825756073</v>
+        <v>0.1478763222694397</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.01968163065612316</v>
+        <v>0.0460260882973671</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.02700474672019482</v>
+        <v>0.1509028375148773</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.01486407220363617</v>
+        <v>0.04935896769165993</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.33025723695755</v>
+        <v>0.09136760234832764</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.06930599361658096</v>
+        <v>0.0878908634185791</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.1289466023445129</v>
+        <v>0.156321108341217</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.05751974135637283</v>
+        <v>0.04634305834770203</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.05229764804244041</v>
+        <v>0.035550557076931</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0971909686923027</v>
+        <v>0.1567597687244415</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.003418691921979189</v>
+        <v>0.01198019459843636</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.05521217733621597</v>
+        <v>0.3223686218261719</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.02634765021502972</v>
+        <v>0.04038859903812408</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.08316390216350555</v>
+        <v>0.02720736898481846</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.03837844729423523</v>
+        <v>0.01511408854275942</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.02017476037144661</v>
+        <v>0.1099507361650467</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.04700367152690887</v>
+        <v>0.005925077013671398</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.02922071889042854</v>
+        <v>0.08571353554725647</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.07032890617847443</v>
+        <v>0.09469672292470932</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.03056284785270691</v>
+        <v>0.02335773594677448</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.09748128801584244</v>
+        <v>0.141162246465683</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.02856041491031647</v>
+        <v>0.04787775129079819</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01247238181531429</v>
+        <v>0.0005673728883266449</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.005575592163950205</v>
+        <v>0.06323613226413727</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.05953821912407875</v>
+        <v>0.07821409404277802</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.1351049542427063</v>
+        <v>0.1338248550891876</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.03408599644899368</v>
+        <v>0.02123909816145897</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.1224398165941238</v>
+        <v>0.2661275267601013</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.1072151809930801</v>
+        <v>0.0867866575717926</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.009004319086670876</v>
+        <v>0.3745772242546082</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.3107121288776398</v>
+        <v>0.03255962207913399</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.02421917766332626</v>
+        <v>0.1813027709722519</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.02224634028971195</v>
+        <v>0.1048236787319183</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.04093867540359497</v>
+        <v>0.05249293893575668</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.03922334313392639</v>
+        <v>0.2441828399896622</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.04368168860673904</v>
+        <v>0.07203660905361176</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.04210484027862549</v>
+        <v>0.06002017110586166</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.03012322075664997</v>
+        <v>0.01446855440735817</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.02834988012909889</v>
+        <v>0.2364170551300049</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.2702050805091858</v>
+        <v>0.1079356819391251</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.1091209799051285</v>
+        <v>0.1204697489738464</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.2837390005588531</v>
+        <v>0.1571215242147446</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.005016971379518509</v>
+        <v>0.06897956877946854</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.04260839521884918</v>
+        <v>0.03465822711586952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0002274368307553232</v>
+        <v>0.001555080176331103</v>
       </c>
       <c r="B6" t="n">
-        <v>0.002842312678694725</v>
+        <v>0.002926177810877562</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0005537428660318255</v>
+        <v>0.0003787856549024582</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001248264918103814</v>
+        <v>0.0002458194503560662</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003785714972764254</v>
+        <v>0.0009451833320781589</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001276548835448921</v>
+        <v>0.002320070983842015</v>
       </c>
       <c r="G6" t="n">
-        <v>4.560861270874739e-05</v>
+        <v>0.001329571707174182</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003948268131352961</v>
+        <v>0.000686943531036377</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0006119605386629701</v>
+        <v>0.000551636447198689</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003415905521251261</v>
+        <v>0.001540274126455188</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0020996427629143</v>
+        <v>0.003691824385896325</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000324185733916238</v>
+        <v>0.0007971620070748031</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00121883861720562</v>
+        <v>0.0003430082579143345</v>
       </c>
       <c r="N6" t="n">
-        <v>0.003263791557401419</v>
+        <v>0.0001348184305243194</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001608444377779961</v>
+        <v>0.002095559844747186</v>
       </c>
       <c r="P6" t="n">
-        <v>6.075628334656358e-05</v>
+        <v>0.001037091482430696</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.665991193382069e-05</v>
+        <v>0.0003612453583627939</v>
       </c>
       <c r="R6" t="n">
-        <v>0.000591812189668417</v>
+        <v>0.001157174352556467</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001927071862155572</v>
+        <v>0.0001583730627316982</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0008358611958101392</v>
+        <v>0.0001705651957308874</v>
       </c>
       <c r="U6" t="n">
-        <v>5.860644159838557e-05</v>
+        <v>0.0005983217852190137</v>
       </c>
       <c r="V6" t="n">
-        <v>5.704358409275301e-05</v>
+        <v>0.0005375967011786997</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0002329255366930738</v>
+        <v>0.0004345491179265082</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0007995855994522572</v>
+        <v>0.0002308568800799549</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0002208547375630587</v>
+        <v>5.478382081491873e-05</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.997774911113083e-06</v>
+        <v>0.000884544919244945</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001119092848966829</v>
+        <v>0.0004938878118991852</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.735377923585474e-05</v>
+        <v>0.0006174821755848825</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0005576619878411293</v>
+        <v>1.799000528990291e-05</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0004668074252549559</v>
+        <v>0.0005854817572981119</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.000523227674420923</v>
+        <v>0.0009062268072739244</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.000417051138356328</v>
+        <v>0.0009218109771609306</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0004930690047331154</v>
+        <v>0.0001246285246452317</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0003192043513990939</v>
+        <v>0.0001114724727813154</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0004054026794619858</v>
+        <v>0.001582397148013115</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0001142564869951457</v>
+        <v>0.0003591072163544595</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0001323239994235337</v>
+        <v>0.0005626218044199049</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0009189156116917729</v>
+        <v>0.0002955715754069388</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0002589547075331211</v>
+        <v>0.0005346976686269045</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0003099441528320312</v>
+        <v>0.0006224518292583525</v>
       </c>
       <c r="AO6" t="n">
-        <v>3.949416714021936e-05</v>
+        <v>5.978687113383785e-05</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0002012979530263692</v>
+        <v>0.000179049777216278</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0002585452166385949</v>
+        <v>0.0003655640466604382</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0001795888529159129</v>
+        <v>0.0006887242197990417</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.0002033628115896136</v>
+        <v>0.0005008934531360865</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0005559030687436461</v>
+        <v>0.001279365969821811</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.002469267696142197</v>
+        <v>0.00193027569912374</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.262283240066608e-05</v>
+        <v>0.0005426728166639805</v>
       </c>
       <c r="AW6" t="n">
-        <v>9.787429007701576e-05</v>
+        <v>0.0001696115941740572</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.001243580016307533</v>
+        <v>0.0004479280323721468</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0006179498159326613</v>
+        <v>0.001016427995637059</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.0007385410717688501</v>
+        <v>7.606831786688417e-05</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.967136429622769e-05</v>
+        <v>0.0006900901207700372</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.00026065728161484</v>
+        <v>0.0004288566124159843</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0002151233056792989</v>
+        <v>3.473708784440532e-05</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.746322469552979e-06</v>
+        <v>0.000661608122754842</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0002784536336548626</v>
+        <v>0.0003893623652402312</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0007011855486780405</v>
+        <v>0.000219214940443635</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.002309906063601375</v>
+        <v>0.0006874499376863241</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0005766526446677744</v>
+        <v>0.00103715481236577</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0006410224596038461</v>
+        <v>0.0007638977840542793</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0002944618172477931</v>
+        <v>0.0003582738572731614</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0008418395882472396</v>
+        <v>0.0004667773318942636</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0002607188071124256</v>
+        <v>5.664580385200679e-06</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0002673990675248206</v>
+        <v>0.0001954011677298695</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0001085572876036167</v>
+        <v>5.657954534399323e-05</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.886858758050948e-05</v>
+        <v>2.402049722149968e-05</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0006700328085571527</v>
+        <v>6.7420449340716e-05</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0004123064572922885</v>
+        <v>0.000145459664054215</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0005967181641608477</v>
+        <v>0.001218429650180042</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0002992984373122454</v>
+        <v>0.0001226180756930262</v>
       </c>
       <c r="BT6" t="n">
-        <v>1.373997656628489e-05</v>
+        <v>0.0007484503439627588</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0003736583166755736</v>
+        <v>0.0004948473651893437</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.001411464298143983</v>
+        <v>0.001394480699673295</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0007006250671111047</v>
+        <v>0.0004938265774399042</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0003437288105487823</v>
+        <v>0.0007957495981827378</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0007515576435253024</v>
+        <v>0.0001792355760699138</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.0002234805142506957</v>
+        <v>0.0007858069147914648</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0002799730864353478</v>
+        <v>8.09437915449962e-05</v>
       </c>
       <c r="CB6" t="n">
-        <v>8.862819231580943e-05</v>
+        <v>0.0002992413647007197</v>
       </c>
       <c r="CC6" t="n">
-        <v>1.08516906038858e-05</v>
+        <v>0.0004379988240543753</v>
       </c>
       <c r="CD6" t="n">
-        <v>6.031539669493213e-05</v>
+        <v>0.0003486833593342453</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.0004898563493043184</v>
+        <v>0.0007177545339800417</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.67646464635618e-05</v>
+        <v>1.523148966953158e-07</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0003042568569071591</v>
+        <v>0.0001660839334363118</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0003928141377400607</v>
+        <v>0.000493630301207304</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.0002538219268899411</v>
+        <v>0.0005836422205902636</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.0002981825091410428</v>
+        <v>0.0005004999693483114</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.873153814813122e-05</v>
+        <v>5.753766345151234e-06</v>
       </c>
       <c r="CL6" t="n">
-        <v>3.546631342032924e-05</v>
+        <v>0.0001869088446255773</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.0004695749667007476</v>
+        <v>8.335633901879191e-05</v>
       </c>
       <c r="CN6" t="n">
-        <v>5.810030415887013e-05</v>
+        <v>0.0005096340901218355</v>
       </c>
       <c r="CO6" t="n">
-        <v>7.823322812328115e-05</v>
+        <v>0.0005989423370920122</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0003192245494574308</v>
+        <v>0.0007376667927019298</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0002108110493281856</v>
+        <v>0.0006257954519242048</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0001337421854259446</v>
+        <v>0.000576362363062799</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0005007900181226432</v>
+        <v>0.0002195420383941382</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0008646589703857899</v>
+        <v>0.0002640102175064385</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0002400052035227418</v>
+        <v>0.0002232550759799778</v>
       </c>
       <c r="CV6" t="n">
-        <v>5.007898289477453e-05</v>
+        <v>0.0002292014542035758</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0002837006468325853</v>
+        <v>0.0007103752577677369</v>
       </c>
       <c r="CX6" t="n">
-        <v>6.833484076196328e-05</v>
+        <v>3.740798274520785e-05</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0003929586382582784</v>
+        <v>0.0001348005753243342</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0004175247449893504</v>
+        <v>0.0003699174267239869</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0003541208279784769</v>
+        <v>0.0005866402061656117</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0001914450549520552</v>
+        <v>0.00026104343123734</v>
       </c>
       <c r="DC6" t="n">
-        <v>9.264302934752777e-05</v>
+        <v>0.0001431918208254501</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.0001328245707554743</v>
+        <v>0.0002104721788782626</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.0004467068647500128</v>
+        <v>0.0004013696452602744</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0007010411354713142</v>
+        <v>0.0008584620663896203</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.0001303248864132911</v>
+        <v>0.0009569424437358975</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.0003451693046372384</v>
+        <v>0.0001645125448703766</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0006655234028585255</v>
+        <v>0.001373945618979633</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0001905207755044103</v>
+        <v>0.002012926852330565</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.0006801380659453571</v>
+        <v>0.0002439047966618091</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0003036634880118072</v>
+        <v>0.0002198404399678111</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0005416590138338506</v>
+        <v>0.0006670381408184767</v>
       </c>
       <c r="DN6" t="n">
-        <v>3.675624611787498e-06</v>
+        <v>0.0004061826912220567</v>
       </c>
       <c r="DO6" t="n">
-        <v>6.670346010650974e-06</v>
+        <v>0.000595730438362807</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.0001021772404783405</v>
+        <v>0.0005286602536216378</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.0008271377300843596</v>
+        <v>0.0003876581322401762</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0001551387686049566</v>
+        <v>0.0002286267699673772</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.0008131394861266017</v>
+        <v>0.001223303959704936</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.0003381199203431606</v>
+        <v>0.0001342648465652019</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.0001366391516057774</v>
+        <v>0.001085417694412172</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.0001257689873455092</v>
+        <v>0.0002834706683643162</v>
       </c>
       <c r="DW6" t="n">
-        <v>2.150515501853079e-05</v>
+        <v>0.0004013553552795202</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0002026146394200623</v>
+        <v>0.0003818647819571197</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0002666743821464479</v>
+        <v>4.236270615365356e-05</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0004754777764901519</v>
+        <v>0.0005905302823521197</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.000254522543400526</v>
+        <v>0.0006432724185287952</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0003256354248151183</v>
+        <v>0.0009027998894453049</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.0001833268033806235</v>
+        <v>7.860464393161237e-05</v>
       </c>
       <c r="ED6" t="n">
-        <v>5.09302262798883e-05</v>
+        <v>0.0004781653406098485</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0002106026513502002</v>
+        <v>0.0007595728384330869</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.0003502616891637444</v>
+        <v>0.0003597733448259532</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.0003298420924693346</v>
+        <v>2.656335709616542e-05</v>
       </c>
       <c r="EH6" t="n">
-        <v>1.003325996862259e-05</v>
+        <v>0.0004428711254149675</v>
       </c>
       <c r="EI6" t="n">
-        <v>1.470805727876723e-06</v>
+        <v>2.669023524504155e-05</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0007090548751875758</v>
+        <v>0.0006441366276703775</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.0001333745021838695</v>
+        <v>0.000137881695991382</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.0004177807713858783</v>
+        <v>0.0003216102195437998</v>
       </c>
       <c r="EM6" t="n">
-        <v>5.799303835374303e-05</v>
+        <v>0.0001848170650191605</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.0002223299234174192</v>
+        <v>1.226093445438892e-05</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.0001526660053059459</v>
+        <v>0.0003398857661522925</v>
       </c>
       <c r="EP6" t="n">
-        <v>5.171928569325246e-05</v>
+        <v>0.0003407009644433856</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.0004832688136957586</v>
+        <v>0.0002317280159331858</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0003497929428704083</v>
+        <v>0.0006684016552753747</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0001730083313304931</v>
+        <v>0.0009134231950156391</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0005536038079299033</v>
+        <v>0.001152540440671146</v>
       </c>
       <c r="EU6" t="n">
-        <v>9.140677138930187e-05</v>
+        <v>2.139890420949087e-05</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.0001338096772087738</v>
+        <v>0.0002696823794394732</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0002382436650805175</v>
+        <v>0.0004468717379495502</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.0001293982932111248</v>
+        <v>0.0002984084712807089</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.0003335376677569002</v>
+        <v>0.000835334649309516</v>
       </c>
       <c r="EZ6" t="n">
-        <v>3.534351344569586e-05</v>
+        <v>6.533803389174864e-05</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0004042098007630557</v>
+        <v>6.727356230840087e-05</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.000321363506373018</v>
+        <v>0.0005775739555247128</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.0003529430250637233</v>
+        <v>0.0005881247343495488</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.0002893572964239866</v>
+        <v>0.0004366275388747454</v>
       </c>
       <c r="FE6" t="n">
-        <v>3.032542372238822e-05</v>
+        <v>4.805744174518622e-05</v>
       </c>
       <c r="FF6" t="n">
-        <v>3.753013152163476e-05</v>
+        <v>5.313144356478006e-06</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.0002083138097077608</v>
+        <v>9.447439515497535e-05</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0002723721554502845</v>
+        <v>0.001329752965830266</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0004337184363976121</v>
+        <v>0.0006824511801823974</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.0005971878999844193</v>
+        <v>0.000127640028949827</v>
       </c>
       <c r="FK6" t="n">
-        <v>8.720748155610636e-05</v>
+        <v>7.699038542341441e-05</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0001772311661625281</v>
+        <v>0.001168602262623608</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.000399072072468698</v>
+        <v>0.0003016819537151605</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.0001588973973412067</v>
+        <v>0.001274357433430851</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.0004462553188204765</v>
+        <v>0.0008296483429148793</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.0001836188894230872</v>
+        <v>0.0004575535422191024</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.0008708111708983779</v>
+        <v>0.0001833353016991168</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0002830611483659595</v>
+        <v>0.001766844652593136</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.001027777325361967</v>
+        <v>0.001090245204977691</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.0001322495809290558</v>
+        <v>0.0003335128130856901</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.0001613296917639673</v>
+        <v>0.0002100188139593229</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0002166579506592825</v>
+        <v>8.621282177045941e-05</v>
       </c>
       <c r="FW6" t="n">
-        <v>8.783623343333602e-06</v>
+        <v>0.0003516277065500617</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.0001913603045977652</v>
+        <v>0.0001402194902766496</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.000210235797567293</v>
+        <v>0.0005392847815528512</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.0003270913730375469</v>
+        <v>0.0006895402912050486</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.0004626896989066154</v>
+        <v>0.0004693649243563414</v>
       </c>
       <c r="GB6" t="n">
-        <v>5.139583299751393e-05</v>
+        <v>0.0001412818965036422</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.0003118437889497727</v>
+        <v>0.001122566754929721</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0002294376754434779</v>
+        <v>0.0008106727618724108</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.0002263431233586743</v>
+        <v>0.0002095148956868798</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0002184889890486374</v>
+        <v>0.0004230214399285614</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0004738817806355655</v>
+        <v>0.001203326624818146</v>
       </c>
     </row>
     <row r="7">
@@ -4413,1709 +4413,5123 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.3584462702274323</v>
+        <v>0.164519727230072</v>
       </c>
       <c r="B8" t="n">
-        <v>1.790201306343079</v>
+        <v>0.2910912334918976</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03772230446338654</v>
+        <v>0.03829114511609077</v>
       </c>
       <c r="D8" t="n">
-        <v>1.041835904121399</v>
+        <v>0.05285286530852318</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6043265461921692</v>
+        <v>0.03630866482853889</v>
       </c>
       <c r="F8" t="n">
-        <v>0.430549681186676</v>
+        <v>0.18751360476017</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7120866775512695</v>
+        <v>0.03923818469047546</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4751811325550079</v>
+        <v>0.1576279401779175</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001221202313899994</v>
+        <v>0.03063321858644485</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3823773562908173</v>
+        <v>0.1961976438760757</v>
       </c>
       <c r="K8" t="n">
-        <v>1.197782397270203</v>
+        <v>0.2015524208545685</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09421571344137192</v>
+        <v>0.004723232239484787</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4771375060081482</v>
+        <v>0.18906469643116</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7639281749725342</v>
+        <v>0.2079351395368576</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8030973672866821</v>
+        <v>0.1922143250703812</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5796977877616882</v>
+        <v>0.09270491451025009</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.06353528797626495</v>
+        <v>0.1375046223402023</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1667407006025314</v>
+        <v>0.09663024544715881</v>
       </c>
       <c r="S8" t="n">
-        <v>0.07327535003423691</v>
+        <v>0.00977766141295433</v>
       </c>
       <c r="T8" t="n">
-        <v>0.09876465797424316</v>
+        <v>0.00962251890450716</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1709635555744171</v>
+        <v>0.06654062867164612</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4820859134197235</v>
+        <v>0.05496019497513771</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6075873374938965</v>
+        <v>0.0216082502156496</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2065392881631851</v>
+        <v>0.02559133432805538</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4466349482536316</v>
+        <v>0.003417733125388622</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2383557856082916</v>
+        <v>0.08088468760251999</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.1928972452878952</v>
+        <v>0.03025046177208424</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1693395972251892</v>
+        <v>0.05175879597663879</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.1042802408337593</v>
+        <v>0.06788168102502823</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.02347533032298088</v>
+        <v>0.01184894889593124</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.1278138756752014</v>
+        <v>0.01247082930058241</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.09040240943431854</v>
+        <v>0.06707485020160675</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.1112780943512917</v>
+        <v>0.0005127610638737679</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.2271540313959122</v>
+        <v>0.008121334947645664</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.1887356340885162</v>
+        <v>0.01466274913400412</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.1286306977272034</v>
+        <v>0.04558226093649864</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.2793288826942444</v>
+        <v>0.03731134906411171</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.3790154755115509</v>
+        <v>0.1122049540281296</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.1124932393431664</v>
+        <v>0.1041678488254547</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002156505361199379</v>
+        <v>0.03436069190502167</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.1991277039051056</v>
+        <v>0.06575696170330048</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.1616044193506241</v>
+        <v>0.0007926621474325657</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.2183799892663956</v>
+        <v>0.02876873314380646</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.1684670001268387</v>
+        <v>0.04633915424346924</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.1297468841075897</v>
+        <v>0.04791688174009323</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.004093416035175323</v>
+        <v>0.1350959539413452</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.110724925994873</v>
+        <v>0.03865728154778481</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.1383942365646362</v>
+        <v>0.08635368943214417</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.5382866263389587</v>
+        <v>0.04996157810091972</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.5033116936683655</v>
+        <v>0.229304626584053</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.3210770189762115</v>
+        <v>0.09409606456756592</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.07106883823871613</v>
+        <v>0.025123480707407</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.2914391756057739</v>
+        <v>0.0151866627857089</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.2396904677152634</v>
+        <v>0.01824883930385113</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.03799057751893997</v>
+        <v>0.05976071581244469</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.3389694690704346</v>
+        <v>0.1084270030260086</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.1788178384304047</v>
+        <v>0.02213738486170769</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.2191516160964966</v>
+        <v>0.003085099160671234</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.2069528251886368</v>
+        <v>0.0385797806084156</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.1195977926254272</v>
+        <v>0.1151559948921204</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.360312819480896</v>
+        <v>0.001346318051218987</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.1519123017787933</v>
+        <v>0.04269149899482727</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.03095497936010361</v>
+        <v>0.05020918324589729</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.3402566611766815</v>
+        <v>0.03135192394256592</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.1517529785633087</v>
+        <v>0.03171591833233833</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.1135684996843338</v>
+        <v>0.03100596368312836</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.1980616897344589</v>
+        <v>0.04150187224149704</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.1419252157211304</v>
+        <v>0.04889028519392014</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01267870515584946</v>
+        <v>0.08588153868913651</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.1334854513406754</v>
+        <v>0.0414985865354538</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.04639210551977158</v>
+        <v>0.03497111052274704</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.1305186897516251</v>
+        <v>0.01535589620471001</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.1040032655000687</v>
+        <v>0.07325120270252228</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.7122942209243774</v>
+        <v>0.06139420345425606</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.05812536180019379</v>
+        <v>0.07227221131324768</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.4522306323051453</v>
+        <v>0.08217879384756088</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.7634901404380798</v>
+        <v>0.05355700105428696</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.2728298604488373</v>
+        <v>0.05328750982880592</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.2957765758037567</v>
+        <v>0.02568615227937698</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.07580991089344025</v>
+        <v>0.04725390672683716</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.2064163386821747</v>
+        <v>0.03537794575095177</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.1682048887014389</v>
+        <v>0.04408587515354156</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.2248909473419189</v>
+        <v>0.08183902502059937</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.1570574045181274</v>
+        <v>0.03716760501265526</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.1033672392368317</v>
+        <v>0.03867398202419281</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.03121338784694672</v>
+        <v>0.01278306730091572</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.2323069274425507</v>
+        <v>0.04081917181611061</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.03103935718536377</v>
+        <v>0.02707915753126144</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.07549037784337997</v>
+        <v>0.04431261867284775</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.199411928653717</v>
+        <v>0.02923525683581829</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.1659461706876755</v>
+        <v>0.05210484564304352</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.112728513777256</v>
+        <v>0.006595004349946976</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.1509620398283005</v>
+        <v>0.1320478916168213</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.2490007281303406</v>
+        <v>0.1727158576250076</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.1439545750617981</v>
+        <v>0.04230509325861931</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.009540528059005737</v>
+        <v>0.08794266730546951</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.4608711004257202</v>
+        <v>0.01451783813536167</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.3410638868808746</v>
+        <v>0.01300796400755644</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.09880004078149796</v>
+        <v>0.001998179592192173</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.1498150378465652</v>
+        <v>0.04539224877953529</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.2329525053501129</v>
+        <v>0.07253868877887726</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0879199355840683</v>
+        <v>0.02140353247523308</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.2085323929786682</v>
+        <v>0.03770418837666512</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0002793781459331512</v>
+        <v>0.005918542854487896</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.3379155099391937</v>
+        <v>0.04857636988162994</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.004541285336017609</v>
+        <v>0.0336032547056675</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.1058250516653061</v>
+        <v>0.05700597167015076</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.1230523809790611</v>
+        <v>0.02970354631543159</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.1563720852136612</v>
+        <v>0.01887183450162411</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0708807110786438</v>
+        <v>0.04533543437719345</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.3108603656291962</v>
+        <v>0.0313464030623436</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.5963927507400513</v>
+        <v>0.007364710792899132</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.2383430600166321</v>
+        <v>0.115970216691494</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.04670080542564392</v>
+        <v>0.07340108603239059</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.4257674217224121</v>
+        <v>0.03079771995544434</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.07314774394035339</v>
+        <v>0.04845866560935974</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.1433699131011963</v>
+        <v>0.09623128920793533</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.2128707766532898</v>
+        <v>0.01505504362285137</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.2631866931915283</v>
+        <v>0.05029629170894623</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.04957582429051399</v>
+        <v>0.01218868046998978</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.1311859339475632</v>
+        <v>0.02484283037483692</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.06307494640350342</v>
+        <v>0.04944676160812378</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.4292253255844116</v>
+        <v>0.09755990654230118</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.02953950315713882</v>
+        <v>0.02253082953393459</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.4973882138729095</v>
+        <v>0.0648648589849472</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.3441393971443176</v>
+        <v>0.02010619267821312</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.1271419078111649</v>
+        <v>0.0410161055624485</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.175093874335289</v>
+        <v>0.009658977389335632</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.3575102090835571</v>
+        <v>0.09184446930885315</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.02353525906801224</v>
+        <v>0.08215197920799255</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.2172643840312958</v>
+        <v>0.1775485128164291</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.326718807220459</v>
+        <v>0.1319113820791245</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.08550725877285004</v>
+        <v>0.04805707186460495</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0259057953953743</v>
+        <v>0.03092013299465179</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.05054126679897308</v>
+        <v>0.07464989274740219</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.01378239691257477</v>
+        <v>0.03803848102688789</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.003021463751792908</v>
+        <v>0.007825536653399467</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.07344658672809601</v>
+        <v>0.09219078719615936</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.1156003549695015</v>
+        <v>0.001890003681182861</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.1927606910467148</v>
+        <v>0.02522866055369377</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.2708601057529449</v>
+        <v>0.03334194794297218</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.08969967067241669</v>
+        <v>0.01040041446685791</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.05691050738096237</v>
+        <v>0.01724170334637165</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.06658905744552612</v>
+        <v>0.05644452944397926</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.04282408952713013</v>
+        <v>0.08843556046485901</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.01389267295598984</v>
+        <v>0.08819305896759033</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.01655787229537964</v>
+        <v>0.08357980102300644</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.004994690418243408</v>
+        <v>0.0002626045607030392</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.2102652192115784</v>
+        <v>0.04194043949246407</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.8129996061325073</v>
+        <v>0.041751429438591</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.1665838062763214</v>
+        <v>0.005435230676084757</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.6360155344009399</v>
+        <v>0.06011602655053139</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.2007069289684296</v>
+        <v>0.09112595021724701</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.1536104828119278</v>
+        <v>0.05969202145934105</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.1353655159473419</v>
+        <v>0.08055218309164047</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.0640292689204216</v>
+        <v>0.0259836558252573</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.1757273375988007</v>
+        <v>0.05083921551704407</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0651281476020813</v>
+        <v>0.01365500595420599</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.2721007168292999</v>
+        <v>0.01971986889839172</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0553864911198616</v>
+        <v>0.02309706062078476</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.07649904489517212</v>
+        <v>0.06507434695959091</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.1292133331298828</v>
+        <v>0.01352178305387497</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.06224418804049492</v>
+        <v>0.02223890088498592</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.1817152798175812</v>
+        <v>0.09023113548755646</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.1365454494953156</v>
+        <v>0.004693608731031418</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.2886818051338196</v>
+        <v>0.03291917219758034</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.06435902416706085</v>
+        <v>0.0590350478887558</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.2184914201498032</v>
+        <v>0.04646223410964012</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.01616152375936508</v>
+        <v>0.05622359365224838</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.01635536551475525</v>
+        <v>0.12454454600811</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.2399944514036179</v>
+        <v>0.0117547120898962</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.03934597223997116</v>
+        <v>0.114818200469017</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.09992217272520065</v>
+        <v>0.1771017760038376</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.3184441328048706</v>
+        <v>0.1520157754421234</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.02179103530943394</v>
+        <v>0.1771628707647324</v>
       </c>
       <c r="FT8" t="n">
-        <v>1.099899768829346</v>
+        <v>0.1956195831298828</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.097757488489151</v>
+        <v>0.001903451513499022</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.05316286534070969</v>
+        <v>0.06454016268253326</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.1861234605312347</v>
+        <v>0.01160693075507879</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.06286634504795074</v>
+        <v>0.0331452265381813</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.1829564720392227</v>
+        <v>0.07436356693506241</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.02320719510316849</v>
+        <v>0.05902305617928505</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.1109287738800049</v>
+        <v>0.07354697585105896</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.1372466683387756</v>
+        <v>0.0147947994992137</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.1084922552108765</v>
+        <v>0.09793338924646378</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.0232217013835907</v>
+        <v>0.009679878130555153</v>
       </c>
       <c r="GE8" t="n">
-        <v>1.025578022003174</v>
+        <v>2.702698111534119e-06</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.04747212305665016</v>
+        <v>0.04073473811149597</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.3383513689041138</v>
+        <v>0.1113265007734299</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.006650473922491074</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.04517903551459312</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001158667262643576</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03780137747526169</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.007590645458549261</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00267395656555891</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008507669903337955</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.006280767265707254</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00415507610887289</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002890365198254585</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04036259651184082</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003952751401811838</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02559362538158894</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01000096742063761</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00609961710870266</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.007696296088397503</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.00621708482503891</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002519732574000955</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.003405079012736678</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.006450075656175613</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004085142631083727</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002301691565662622</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0007140262750908732</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.007053637877106667</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001908305799588561</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.006322821602225304</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.005255405325442553</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001429782714694738</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.005192716140300035</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.003710927907377481</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.009953509084880352</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.004648717120289803</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.004898696672171354</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0003261397359892726</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.003268431173637509</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.002968828659504652</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.001409509219229221</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.008676823228597641</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0005848662694916129</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.00213992060162127</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.003023987635970116</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.003695477498695254</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.002187121426686645</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.001404643524438143</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.003895334200933576</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.009956039488315582</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.02984884008765221</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.001448214869014919</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.02076743915677071</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.004966715350747108</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0005126604228280485</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.001499284408055246</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.002207892015576363</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.00273928209207952</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.004331700969487429</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.007981556467711926</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.01034763548523188</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.002989191096276045</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.01465189643204212</v>
+        <v>0</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.005480934400111437</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.004431193228811026</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.006547395139932632</v>
+        <v>0</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0005314149893820286</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.005327035672962666</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.001511877751909196</v>
+        <v>0</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.00324410549364984</v>
+        <v>0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0001263999147340655</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001708510331809521</v>
+        <v>0</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.005709484685212374</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.002634902484714985</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0008641996537335217</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.001760450890287757</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.00973074696958065</v>
+        <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.01565752550959587</v>
+        <v>0</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0006670544971711934</v>
+        <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.00549229932948947</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.003493249183520675</v>
+        <v>0</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.005090160295367241</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.002375452313572168</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.002616409910842776</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.005686879623681307</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.001753511256538332</v>
+        <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.006571813486516476</v>
+        <v>0</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.00280322995968163</v>
+        <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.007081395480781794</v>
+        <v>0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.002637945581227541</v>
+        <v>0</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002155889291316271</v>
+        <v>0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.00142458884511143</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.0007190531468950212</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.003901534015312791</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.01067361608147621</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.000696871371474117</v>
+        <v>0</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.003555400064215064</v>
+        <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.001774667645804584</v>
+        <v>0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.002100872807204723</v>
+        <v>0</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.01052268128842115</v>
+        <v>0</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.01059695519506931</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.01090771704912186</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0019631611648947</v>
+        <v>0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.001923168427310884</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.006287897005677223</v>
+        <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.004511800594627857</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.008428126573562622</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.002217772882431746</v>
+        <v>0</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.001882764976471663</v>
+        <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0009030061773955822</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.001947586191818118</v>
+        <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.002695522271096706</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.002601590938866138</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0137339998036623</v>
+        <v>0</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.001360094174742699</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.02018324285745621</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.01842643879354</v>
+        <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0002064525033347309</v>
+        <v>0</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.01242582034319639</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.006826404482126236</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0005279461620375514</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.002182961441576481</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0003410240169614553</v>
+        <v>0</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.005004147067666054</v>
+        <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0002064256987068802</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0001148253213614225</v>
+        <v>0</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.00253674853593111</v>
+        <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>8.912489283829927e-05</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0006449827924370766</v>
+        <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.004697220865637064</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.001338845351710916</v>
+        <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0006436145631596446</v>
+        <v>0</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.00677150534465909</v>
+        <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.004949093330651522</v>
+        <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.001740171108394861</v>
+        <v>0</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.001502810628153384</v>
+        <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.005648175254464149</v>
+        <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0005632623215205967</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.004906668327748775</v>
+        <v>0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.002882678061723709</v>
+        <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.00640381220728159</v>
+        <v>0</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.005558911710977554</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.006705512292683125</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.003293289337307215</v>
+        <v>0</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.002587767317891121</v>
+        <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.001592344604432583</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.00162488513160497</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.002930282382294536</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.003683761693537235</v>
+        <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.006361368112266064</v>
+        <v>0</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.00693309772759676</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.007024113554507494</v>
+        <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.003318948438391089</v>
+        <v>0</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.01102184690535069</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.004269557073712349</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.003255891613662243</v>
+        <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.002277483697980642</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.001048530451953411</v>
+        <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.006853207480162382</v>
+        <v>0</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.00330025190487504</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.008025646209716797</v>
+        <v>0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.003293920075520873</v>
+        <v>0</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.001945237629115582</v>
+        <v>0</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.002086658962070942</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.002047065878286958</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.003285499289631844</v>
+        <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.001986041432246566</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.003666645614430308</v>
+        <v>0</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.001954708248376846</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.00404489366337657</v>
+        <v>0</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.00121654337272048</v>
+        <v>0</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.006176939699798822</v>
+        <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.003329348051920533</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.00119365646969527</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0001249221386387944</v>
+        <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.001697267056442797</v>
+        <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.007298729382455349</v>
+        <v>0</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.01185742765665054</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.003118273569270968</v>
+        <v>0</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.001010352512821555</v>
+        <v>0</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.004470323212444782</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.0009519205195829272</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.004712838679552078</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.003747039008885622</v>
+        <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.001419703243300319</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.002678088843822479</v>
+        <v>0</v>
       </c>
       <c r="GA9" t="n">
-        <v>8.661659376230091e-05</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.00361375673674047</v>
+        <v>0</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.004935003351420164</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.003754241392016411</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.01914030313491821</v>
+        <v>0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.004267092328518629</v>
+        <v>0</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.003734419122338295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>0.01608192548155785</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.6370885968208313</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.1852567046880722</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.1815700232982635</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.03649497032165527</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.6479909420013428</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.1678467839956284</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.3446798920631409</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.0004563629627227783</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.08376368880271912</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.6945977210998535</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.1947964131832123</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.03421927988529205</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.2331625521183014</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.6340885162353516</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.1465124487876892</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.01128651946783066</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.1232214197516441</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.01851820200681686</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.1497913002967834</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.02562834322452545</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2372777014970779</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1506542265415192</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.04610514640808105</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.04969429224729538</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>0.01312430948019028</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>0.0999259278178215</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>0.06937427818775177</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>0.05075779557228088</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>0.111769400537014</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>0.01258222758769989</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>0.2681594789028168</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>0.07263479381799698</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>0.03899786621332169</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>0.3310569226741791</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>0.1081272810697556</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>0.03798951953649521</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>0.1479515880346298</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>0.008022944442927837</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>0.1388414800167084</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>0.06105620041489601</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>0.02782496251165867</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>0.1239977851510048</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>0.1402633637189865</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>0.01713716052472591</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>0.03131244331598282</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>0.787236213684082</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>0.1595818251371384</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>0.002183437347412109</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>0.07266448438167572</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>0.2389876991510391</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>0.1260489821434021</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>0.1687386780977249</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>0.02218088507652283</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>0.03435241430997849</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>0.1662690937519073</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>0.08702008426189423</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>0.2266446501016617</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>0.1990565210580826</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>0.02766750007867813</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>0.1821816712617874</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>0.09820650517940521</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>0.1108866110444069</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>0.002543177455663681</v>
       </c>
       <c r="BM10" t="n">
-        <v>0</v>
+        <v>0.1206213682889938</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>0.04738908261060715</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>0.08251069486141205</v>
       </c>
       <c r="BP10" t="n">
-        <v>0</v>
+        <v>0.128577783703804</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0</v>
+        <v>0.2290943711996078</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>0.1105635315179825</v>
       </c>
       <c r="BS10" t="n">
-        <v>0</v>
+        <v>0.1327435076236725</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>0.1036128997802734</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>0.048624437302351</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>0.6770340204238892</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>0.006543387193232775</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>0.3828334808349609</v>
       </c>
       <c r="BY10" t="n">
-        <v>0</v>
+        <v>0.03817062452435493</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>0.1990504264831543</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>0.03059877827763557</v>
       </c>
       <c r="CB10" t="n">
-        <v>0</v>
+        <v>0.02451442927122116</v>
       </c>
       <c r="CC10" t="n">
-        <v>0</v>
+        <v>0.1634667962789536</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>0.05447129905223846</v>
       </c>
       <c r="CE10" t="n">
-        <v>0</v>
+        <v>0.1863354742527008</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>0.01846787147223949</v>
       </c>
       <c r="CG10" t="n">
-        <v>0</v>
+        <v>0.01768388599157333</v>
       </c>
       <c r="CH10" t="n">
-        <v>0</v>
+        <v>0.0381946973502636</v>
       </c>
       <c r="CI10" t="n">
-        <v>0</v>
+        <v>0.1502912640571594</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0</v>
+        <v>0.0429532416164875</v>
       </c>
       <c r="CK10" t="n">
-        <v>0</v>
+        <v>0.03641523420810699</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>0.007557366508990526</v>
       </c>
       <c r="CM10" t="n">
-        <v>0</v>
+        <v>0.07675236463546753</v>
       </c>
       <c r="CN10" t="n">
-        <v>0</v>
+        <v>0.3193584680557251</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>0.01512334123253822</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>0.2128839194774628</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0</v>
+        <v>0.1148883104324341</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>0.1467050015926361</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>0.0308802742511034</v>
       </c>
       <c r="CT10" t="n">
-        <v>0</v>
+        <v>0.05368739366531372</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>0.06011616438627243</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>0.005364099517464638</v>
       </c>
       <c r="CW10" t="n">
-        <v>0</v>
+        <v>0.1726389527320862</v>
       </c>
       <c r="CX10" t="n">
-        <v>0</v>
+        <v>0.0467102974653244</v>
       </c>
       <c r="CY10" t="n">
-        <v>0</v>
+        <v>0.00354459136724472</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0</v>
+        <v>0.0144488513469696</v>
       </c>
       <c r="DA10" t="n">
-        <v>0</v>
+        <v>0.1472101211547852</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>0.02351837046444416</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>0.02215620502829552</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>0.007749659009277821</v>
       </c>
       <c r="DE10" t="n">
-        <v>0</v>
+        <v>0.04752084985375404</v>
       </c>
       <c r="DF10" t="n">
-        <v>0</v>
+        <v>0.4092320799827576</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>0.06246131286025047</v>
       </c>
       <c r="DH10" t="n">
-        <v>0</v>
+        <v>0.02953255921602249</v>
       </c>
       <c r="DI10" t="n">
-        <v>0</v>
+        <v>0.1327601969242096</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>0.2079386711120605</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>0.0346987396478653</v>
       </c>
       <c r="DL10" t="n">
-        <v>0</v>
+        <v>0.2755046188831329</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>0.4544413089752197</v>
       </c>
       <c r="DN10" t="n">
-        <v>0</v>
+        <v>0.07449106127023697</v>
       </c>
       <c r="DO10" t="n">
-        <v>0</v>
+        <v>0.102531298995018</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>0.06298249214887619</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>0.127545177936554</v>
       </c>
       <c r="DR10" t="n">
-        <v>0</v>
+        <v>0.1269629150629044</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>0.06481899321079254</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>0.07717515528202057</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>0.179262787103653</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>0.03156150132417679</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>0.07774791121482849</v>
       </c>
       <c r="DX10" t="n">
-        <v>0</v>
+        <v>0.03388193622231483</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>0.1436312943696976</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0</v>
+        <v>0.08208043128252029</v>
       </c>
       <c r="EA10" t="n">
-        <v>0</v>
+        <v>0.07369548082351685</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>0.07588572800159454</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>0.02977171912789345</v>
       </c>
       <c r="ED10" t="n">
-        <v>0</v>
+        <v>0.07915227115154266</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>0.2788826823234558</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>0.04264103621244431</v>
       </c>
       <c r="EG10" t="n">
-        <v>0</v>
+        <v>0.1120264604687691</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>0.070632703602314</v>
       </c>
       <c r="EI10" t="n">
-        <v>0</v>
+        <v>0.07616760581731796</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0</v>
+        <v>0.08567081391811371</v>
       </c>
       <c r="EK10" t="n">
-        <v>0</v>
+        <v>0.004193633794784546</v>
       </c>
       <c r="EL10" t="n">
-        <v>0</v>
+        <v>0.02374584414064884</v>
       </c>
       <c r="EM10" t="n">
-        <v>0</v>
+        <v>0.01686547324061394</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>0.03573068231344223</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>0.04814672470092773</v>
       </c>
       <c r="EP10" t="n">
-        <v>0</v>
+        <v>0.1613365411758423</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>0.0106293261051178</v>
       </c>
       <c r="ER10" t="n">
-        <v>0</v>
+        <v>0.1012239083647728</v>
       </c>
       <c r="ES10" t="n">
-        <v>0</v>
+        <v>0.2462056428194046</v>
       </c>
       <c r="ET10" t="n">
-        <v>0</v>
+        <v>0.2832415401935577</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>0.07796578854322433</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>0.09365899860858917</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>0.09980501234531403</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>0.02878996171057224</v>
       </c>
       <c r="EY10" t="n">
-        <v>0</v>
+        <v>0.2245486229658127</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>0.02810476534068584</v>
       </c>
       <c r="FA10" t="n">
-        <v>0</v>
+        <v>0.004057973623275757</v>
       </c>
       <c r="FB10" t="n">
-        <v>0</v>
+        <v>0.01038060989230871</v>
       </c>
       <c r="FC10" t="n">
-        <v>0</v>
+        <v>0.1671509593725204</v>
       </c>
       <c r="FD10" t="n">
-        <v>0</v>
+        <v>0.07003860175609589</v>
       </c>
       <c r="FE10" t="n">
-        <v>0</v>
+        <v>0.02592700906097889</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>0.0748373419046402</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>0.01636502705514431</v>
       </c>
       <c r="FH10" t="n">
-        <v>0</v>
+        <v>0.1921595335006714</v>
       </c>
       <c r="FI10" t="n">
-        <v>0</v>
+        <v>0.1009607836604118</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0</v>
+        <v>0.09209340065717697</v>
       </c>
       <c r="FK10" t="n">
-        <v>0</v>
+        <v>0.08032317459583282</v>
       </c>
       <c r="FL10" t="n">
-        <v>0</v>
+        <v>0.1744464337825775</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>0.07429448515176773</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>0.5001020431518555</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>0.1697664707899094</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>0.1172070354223251</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0</v>
+        <v>0.07976420223712921</v>
       </c>
       <c r="FR10" t="n">
-        <v>0</v>
+        <v>0.005239587277173996</v>
       </c>
       <c r="FS10" t="n">
-        <v>0</v>
+        <v>0.3764907121658325</v>
       </c>
       <c r="FT10" t="n">
-        <v>0</v>
+        <v>0.09564844518899918</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>0.2189303487539291</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>0.1422827392816544</v>
       </c>
       <c r="FW10" t="n">
-        <v>0</v>
+        <v>0.6384300589561462</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>0.04171144217252731</v>
       </c>
       <c r="FY10" t="n">
-        <v>0</v>
+        <v>0.1255362033843994</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0</v>
+        <v>0.08802007883787155</v>
       </c>
       <c r="GA10" t="n">
-        <v>0</v>
+        <v>0.1511224657297134</v>
       </c>
       <c r="GB10" t="n">
-        <v>0</v>
+        <v>0.06423849612474442</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>0.01053828839212656</v>
       </c>
       <c r="GD10" t="n">
-        <v>0</v>
+        <v>0.1126859337091446</v>
       </c>
       <c r="GE10" t="n">
-        <v>0</v>
+        <v>0.04994548484683037</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>0.07437960058450699</v>
       </c>
       <c r="GG10" t="n">
-        <v>0</v>
+        <v>0.09074144065380096</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.3053070306777954</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1.024810314178467</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.3999378681182861</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.04239234328269958</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0418567955493927</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1900943517684937</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.161759689450264</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2131717801094055</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.281107097864151</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.2226627916097641</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.184573650360107</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4322545528411865</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.05619454383850098</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1244781464338303</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.04684514179825783</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.2999694049358368</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3605938255786896</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3705161213874817</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.03352553024888039</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.1580840796232224</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.03158777952194214</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1175255477428436</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.07654199004173279</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.110119640827179</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.07848295569419861</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.04864765703678131</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.1137926131486893</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.2190489172935486</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.03335890918970108</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.1019022464752197</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.1001994833350182</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.03432971611618996</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.1622089296579361</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.008967101573944092</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.07447530329227448</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.03955154120922089</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.08913584053516388</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.2976326942443848</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.03474642708897591</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.08044295012950897</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.4309557378292084</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.02177852764725685</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.06688721477985382</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.1269041001796722</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.1152516752481461</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.3683028221130371</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.6574726104736328</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.04206394776701927</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.1007042601704597</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.05879038944840431</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.1323185861110687</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.1674389243125916</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.0302828811109066</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.05361837148666382</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.0359477624297142</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.1188474074006081</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.3881483674049377</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.113847091794014</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.4026094973087311</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.3273108601570129</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.1276762932538986</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.307393491268158</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.1635840535163879</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.0005507469177246094</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.3437023162841797</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.08531168103218079</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.1326572149991989</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.1971199512481689</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.02954911813139915</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.06872303783893585</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.009313119575381279</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.1145651936531067</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0.02452827990055084</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.6282081007957458</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.02738987095654011</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.2503397464752197</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.1118469908833504</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.01299116387963295</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.01353074237704277</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.06154284626245499</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.1282877773046494</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.0851910412311554</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.3962256610393524</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.04653162136673927</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.0113784447312355</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.07750821113586426</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.05664957314729691</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.03987515717744827</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.001185230910778046</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0.03208668157458305</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.030116006731987</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.3246998190879822</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.1900920867919922</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.2155369520187378</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.2522740364074707</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.08689472824335098</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0.1023837104439735</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0.2411076724529266</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0.02390891686081886</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0.04081469029188156</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.3824663758277893</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0.07934211194515228</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.01510222256183624</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.05052429065108299</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0.04329925030469894</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0.03372594714164734</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0.01739629358053207</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0.1056582853198051</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.1727271974086761</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.2880071401596069</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0.03414042294025421</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.04707560688257217</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.3266145288944244</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0.185854360461235</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0.1807494312524796</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.2047096788883209</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0.01100060343742371</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.1456583738327026</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.1317713260650635</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0.1179688423871994</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.1368528604507446</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.05998378619551659</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.08200930058956146</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.05024466663599014</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0.01403453201055527</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0.07336295396089554</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.20681032538414</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.1782971173524857</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0.05653555691242218</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.07621392607688904</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.2185130715370178</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.07191098481416702</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0.1104236468672752</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0.09882760792970657</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0.3963969051837921</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0.09886369109153748</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.2875284552574158</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0.08972425758838654</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.07586184144020081</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.1003536209464073</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.08354754000902176</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0.02029496990144253</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0.09318599849939346</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0.05515773221850395</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0.1454349160194397</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.2048032432794571</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0.0299043208360672</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.08128894865512848</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.06263360381126404</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.03550313785672188</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0.08979301154613495</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0.09199940413236618</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0.2723581194877625</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0.1053077504038811</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.3954868614673615</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0.0749162882566452</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.03402999043464661</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.05939039215445518</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0.05287589132785797</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0.02667572349309921</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0.007142212241888046</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0.082609623670578</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0.01691031083464622</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.2748020589351654</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0.07915195822715759</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.1335140913724899</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.0679653212428093</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0.07178083807229996</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0.1270575076341629</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0.02948762103915215</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0.10960803180933</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0.03195801377296448</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.4149098098278046</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0.1763548105955124</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.2320059388875961</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.187358170747757</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0.3131711781024933</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0.2000998854637146</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0.3167441785335541</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0.01452652364969254</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0.1863792389631271</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.3207190632820129</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0.04651709645986557</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0.0251137986779213</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0.01031355559825897</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.2150067090988159</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0.03543741628527641</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0.04142503812909126</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0.1845896691083908</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.318374409642331e-09</v>
+      </c>
+      <c r="B12" t="n">
+        <v>6.662817519931252e-11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.056797649390262e-09</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.627815660043552e-09</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.157379913076852e-10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.696999762934581e-09</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.045604129476743e-10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.463030335242422e-10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6.576328370755391e-10</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8.109522497967703e-10</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.857001107387958e-10</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.675441119175503e-09</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.049581225906707e-10</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.267616508599417e-10</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.145279648895325e-09</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.251597603335597e-09</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.645938828622519e-10</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.458850151792035e-09</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.934209790225964e-10</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.557599853072247e-10</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.906010987402396e-10</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5.514697032360516e-11</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.216716740721658e-11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.202404786322276e-10</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.675344945579639e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.281601627744493e-11</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.830732315217688e-10</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.046171149710062e-09</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>6.462734236656331e-10</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.611244249133392e-09</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.879586569193293e-10</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>5.535539249201804e-10</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>7.092073039949298e-10</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>7.459480255711526e-10</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.996900908518562e-11</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>9.585191668159965e-11</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.024747953159988e-09</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.402827936620611e-10</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2.661526554703642e-10</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>5.433807570565108e-11</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.030688756564757e-09</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>4.483170501501377e-10</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.729721921250871e-10</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>6.430727478301534e-12</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.640428596935919e-10</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.084302758691535e-09</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.076036453857455e-09</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.466163301877543e-10</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5.266720948249315e-10</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.022232631875397e-09</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.396702864475685e-09</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>3.030767581346794e-10</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.539078669538952e-10</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>3.114720703578655e-10</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.983613828748787e-10</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.279348709777196e-09</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.961388717055314e-10</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.023619494195827e-09</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>5.644762435252915e-10</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1.720730002929827e-09</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>5.647854961488008e-10</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>2.930853892912921e-10</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>4.329380604017885e-11</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>3.278519122851264e-11</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>4.894027405555335e-10</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>3.401517401080412e-10</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.473149380259997e-11</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1.086177675579947e-11</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>4.751795068536069e-10</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1.037720576135825e-09</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>2.114257102725503e-10</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>3.561413108865707e-10</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>5.98905813831152e-10</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>7.378387900658367e-10</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>4.476152781762721e-10</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>4.404391851231537e-10</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.139809802097602e-09</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>4.370154238486634e-10</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>4.119732888163696e-10</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>6.487838044577643e-10</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>7.058845730156804e-10</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>2.868773829600713e-10</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>3.442881535420383e-10</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>1.310522523834123e-10</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>1.878450450742974e-10</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>3.199299991596405e-10</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>3.674675563836161e-10</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>3.408476834110274e-10</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>7.114421551879246e-11</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>7.745681873672083e-11</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>7.418011760407239e-10</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>4.58531684843777e-10</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.215483269589868e-11</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>7.324368889172206e-11</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>2.586508562885115e-09</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>4.124060537513685e-10</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>2.858257519555707e-10</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>8.125067285646992e-10</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>4.549100540707229e-10</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>2.37737746155986e-10</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>9.762202157759248e-11</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>2.506098384369437e-10</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>1.692188056345856e-11</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>2.588042835593996e-10</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>3.909689239023351e-10</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>2.172319268911593e-10</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>2.016751071698408e-10</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>2.98844032853296e-10</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>1.024643370151068e-09</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>1.097995805388052e-09</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>7.000918733623962e-10</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>1.734954679921685e-10</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>7.502193311026417e-10</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>1.063244381427353e-09</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>7.785050382125291e-10</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>1.139134009342513e-09</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>1.77224013242494e-09</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>9.606311301979531e-10</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>8.403254758704293e-10</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>3.830255904113677e-11</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>1.072578581506889e-09</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>9.625126390355732e-11</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>9.455762839394311e-10</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>1.467838767199581e-10</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>9.554553676016653e-11</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>3.34398897461341e-10</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>3.363393452637808e-10</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>3.115367686046255e-11</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>3.318442465261029e-10</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>1.065517118981063e-09</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>2.213225602787361e-09</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>9.979865822629108e-10</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>2.044594771266617e-10</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>2.475496717335712e-11</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>7.747633090637862e-11</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>4.897344196841402e-10</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>9.710758863690216e-10</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>3.955431537860932e-10</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>6.120315365620854e-10</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>5.725012131030383e-10</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>4.794906138805288e-10</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>1.791457121536055e-10</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>7.486097852726914e-10</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>2.927132702890134e-10</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>2.286291433950538e-10</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>4.872986458792639e-10</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>5.120618373766206e-10</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>3.85070933472953e-11</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>6.122144458053924e-11</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>6.934094409771774e-10</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>5.242697942442476e-10</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>2.703534895953652e-10</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>2.837309831527079e-10</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>3.957625893669103e-10</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>1.320484416256207e-10</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>2.063469534130391e-10</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>1.65350108605189e-10</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>2.578191826696496e-10</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>3.846407636842741e-10</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>2.760613126984168e-10</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>2.612663418943839e-10</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>1.321366349671393e-10</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>2.192195591721458e-10</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>1.812027472514188e-10</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>1.191185483584434e-09</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>1.338252064719825e-09</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>2.765678797089777e-10</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>3.88839516141104e-10</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>5.194484599402305e-12</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>7.221555575753769e-10</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>4.96352514645082e-10</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>2.630440532058742e-09</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>1.996566661999211e-10</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>1.978554431403268e-09</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>2.657938980021868e-09</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>4.852358514995103e-10</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>4.342763648690351e-10</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>1.059435178474288e-10</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>6.053201828670751e-10</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>2.94092805663837e-10</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>3.658846281506811e-10</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>6.076429914791959e-10</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>4.283328691734312e-10</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>1.38512618041986e-10</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>6.929401497046683e-10</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>9.73610303489636e-10</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>7.00441316059397e-10</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>1.024827667173156e-09</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>1.482864525614858e-11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.01526685617864132</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.1104164570569992</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.03915920481085777</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.05980969220399857</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.01471230387687683</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.04583827033638954</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.02809196338057518</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.02903114072978497</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.001585606369189918</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.0262015201151371</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.1090827137231827</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.04923385754227638</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.09839256852865219</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.01860536262392998</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.03148121014237404</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.02648929506540298</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.01360314339399338</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.004863918293267488</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.002838442102074623</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.01306679099798203</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.004979314748197794</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.01239843666553497</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.006341001484543085</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.02028848230838776</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.0009565949440002441</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.003912464715540409</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.01460611540824175</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.01375366933643818</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.02493593096733093</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.01675197295844555</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.01852449029684067</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.02043157443404198</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.03574221581220627</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.00794859416782856</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.01372397691011429</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.0001240806886926293</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.001606923062354326</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.03204407915472984</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.02345204539597034</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.0203978605568409</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.02857705019414425</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.02320954948663712</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.006857470609247684</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.005069214850664139</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.007871625013649464</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.01466220524162054</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.07037700712680817</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.007661094423383474</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.03570327535271645</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.03738436102867126</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.02091744169592857</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.001423442270606756</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.004231593571603298</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.01628054305911064</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.003791915951296687</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.008589585311710835</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.02074039168655872</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.004082960542291403</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.02296649105846882</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.01245155371725559</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.0112621271982789</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.002050835872069001</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.003772719297558069</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.005019074305891991</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.004875375889241695</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.01467346213757992</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.006358156446367502</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.00519341416656971</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.01215452142059803</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.005523729138076305</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.009230677969753742</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.001009899075143039</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.009257313795387745</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.03053678572177887</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0.01296614017337561</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.03419383615255356</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.02341492474079132</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.02954914048314095</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.01168145518749952</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0.001262972597032785</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.009227289818227291</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.003685991279780865</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.03662460669875145</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.01266831066459417</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.02409317530691624</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.006432115100324154</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.009442882612347603</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.00312040327116847</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.008004420436918736</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.001854132628068328</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.007928036153316498</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.01188086904585361</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0.02331149391829967</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.04195278510451317</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.02639610506594181</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.006940268911421299</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.01136073749512434</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.004612887278199196</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0.006178830284625292</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0.006475715897977352</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.03462018817663193</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0.01117033790796995</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.02678970992565155</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.001093513332307339</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.01186578627675772</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0.002462426666170359</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0.007097081281244755</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0.004070159513503313</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.009955181740224361</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.0309537835419178</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0.0207495205104351</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.01832233555614948</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.003063562326133251</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0.06168028712272644</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0.0023178665433079</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.0386943481862545</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0.01603740453720093</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.001781703205779195</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.02452163770794868</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0.01215937361121178</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.009473685175180435</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.01046437863260508</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.01501096785068512</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.01027827989310026</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0.008912616409361362</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0.02786396630108356</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.008355151861906052</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.007489343639463186</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0.02179277688264847</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.003640133421868086</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.02003922685980797</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0.01846669986844063</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0.002072572708129883</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0.0383889339864254</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0.02994366735219955</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0.00661130528897047</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.04043812304735184</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0.004041614010930061</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.02102775685489178</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.0002953927614726126</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.005656342953443527</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0.005182630848139524</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0.002408557571470737</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0.002499211113899946</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0.008686322718858719</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.01664871536195278</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0.004696873482316732</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.02355377562344074</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.004013562109321356</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.0122225284576416</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0.01346881873905659</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0.0108178649097681</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0.01469323039054871</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0.00677770609036088</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.0426161102950573</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0.01189038250595331</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.02916240319609642</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.001904482953250408</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0.01490645948797464</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0.00100335362367332</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0.01033070683479309</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0.004075481090694666</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0.007464648224413395</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.01446522772312164</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0.002376738702878356</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.02209069207310677</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.02182946912944317</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.01672709174454212</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0.00528826517984271</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0.00508368294686079</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0.004778068512678146</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0.01047239080071449</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.0419636145234108</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0.007800957188010216</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.002945425920188427</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.02075117453932762</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0.01874557323753834</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0.003417791798710823</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0.003347046673297882</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0.03419788926839828</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0.004249195568263531</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.01438778266310692</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0.01599163375794888</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0.01177892461419106</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0.01523905713111162</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0.00707943132147193</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0.01449060067534447</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0.01397612225264311</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0.003564069047570229</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.1151178181171417</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.02515168488025665</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.07923374325037003</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.007261611521244049</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.09647350013256073</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.09857216477394104</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01078674849122763</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.07053659111261368</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.03637116402387619</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.1285855323076248</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.05166640505194664</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.1059044748544693</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.008782554417848587</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.09902427345514297</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.1550656706094742</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.02310679294168949</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.0877964198589325</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.0605570487678051</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.0168573409318924</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.01413782685995102</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.03566082194447517</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.016048613935709</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.01727185398340225</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.01031840778887272</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.01566247083246708</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.009384613484144211</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.005201594904065132</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.01741763018071651</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.004986005369573832</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.03907699882984161</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.01585406810045242</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.009870286099612713</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.006453095003962517</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.02086331322789192</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.006460529752075672</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.03586433455348015</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.0137232718989253</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.02429819479584694</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.01149876043200493</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.02466045878827572</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.02815171703696251</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.01561622601002455</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.0009515788406133652</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.008583254180848598</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.007752648554742336</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.09219495207071304</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.06115963310003281</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.06472180783748627</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.004368022084236145</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.03016397356987</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.1203581541776657</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.01861659809947014</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.02866955660283566</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.001561513170599937</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.004581019282341003</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.04935336485505104</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.0004732341622002423</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.004993346519768238</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.05362113192677498</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.02281448990106583</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.009796088561415672</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.01803648471832275</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.0181635320186615</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.02946934662759304</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.04796415567398071</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.0521378293633461</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.02088481374084949</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.01266027614474297</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.002418446587398648</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.02014477178454399</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.00969837699085474</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.01635593548417091</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0.04324650391936302</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.02135738916695118</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.032903041690588</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0.01124527771025896</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.03145266324281693</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0.06018213555216789</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0.02100146934390068</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0.02112741209566593</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.00693238340318203</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0.02492556720972061</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.004274093545973301</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.02618206478655338</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.006052904296666384</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.01604541018605232</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.01886041276156902</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.00655027199536562</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.00402883579954505</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0.005631063133478165</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>8.06380994617939e-05</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.01114315539598465</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0.01326886750757694</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.01755576953291893</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.004751486703753471</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.02599105052649975</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0.02114804647862911</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0.02585570700466633</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0.002538922242820263</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0.03041250444948673</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0.01360911410301924</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0.02903647348284721</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.007667327765375376</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.03046571463346481</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.02481253631412983</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0.004725833423435688</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0.0007633727509528399</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0.005929550155997276</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.05079949274659157</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0.04443949460983276</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.03875533491373062</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0.02070177718997002</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.02421762049198151</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.007962272502481937</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0.02273354306817055</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.00370401912368834</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0.03398779779672623</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.007994608953595161</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0.02596706338226795</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0.018570177257061</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0.01207983121275902</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0.03772436454892159</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.02979069203138351</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0.01313739642500877</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0.006016120780259371</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0.0190044678747654</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0.01179111562669277</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0.02269647642970085</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0.01771534793078899</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0.07133878022432327</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.02020271122455597</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.04564498737454414</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>0.007818982005119324</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0.004879039246588945</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0.003085893345996737</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0.01270466577261686</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>0.005432846024632454</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0.02812284976243973</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0.01448633335530758</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.0338268093764782</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0.001300820265896618</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0.002988615771755576</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0.0132645508274436</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0.00703440373763442</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0.006687209475785494</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.01571092009544373</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0.001897174632176757</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0.01041076239198446</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.001042844960466027</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.02113026566803455</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0.02440512180328369</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0.01771530508995056</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0.007320038042962551</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0.02812285348773003</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0.003498959355056286</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0.0220938790589571</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0.003923376090824604</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.02180980145931244</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.02821231447160244</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0.01242471672594547</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0.004480320960283279</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0.00306329969316721</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0.03379720821976662</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.01215015817433596</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0.03896286338567734</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0.06160922721028328</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.0296518187969923</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.02674173936247826</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0.01878849603235722</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0.03142547234892845</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0.0195534210652113</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0.02075236290693283</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.06087496876716614</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0.04594330489635468</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0.01070816069841385</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.02149737253785133</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0.05005604028701782</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0.02689480781555176</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0.02015566825866699</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0.03325366228818893</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0.01419391389936209</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0.008020665496587753</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0.04161898046731949</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0.007628741674125195</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0.02764260023832321</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.01251223683357239</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>0.01198777742683887</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>0.01011937484145164</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0.008697935380041599</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3.18710517603904e-05</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.00022835039999336</v>
+      </c>
+      <c r="C15" t="n">
+        <v>7.714163803029805e-05</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.756756243295968e-05</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3.563649806892499e-05</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.0003024507313966751</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8.104086737148464e-05</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0001013025685097091</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6.750251486664638e-05</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.544955688994378e-06</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0003150433476548642</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9.133997082244605e-06</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0001076634143828414</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.271103873383254e-05</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0003960079047828913</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.72666075034067e-05</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.091886173933744e-05</v>
+      </c>
+      <c r="R15" t="n">
+        <v>8.00576017354615e-05</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.362865001894534e-05</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.063494321191683e-05</v>
+      </c>
+      <c r="U15" t="n">
+        <v>8.699856698513031e-05</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.287989577278495e-05</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.498637357144617e-05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.928996011381969e-05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.283397381892428e-05</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.0001445845555281267</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.578524799901061e-06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.510532355401665e-05</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.465604459051974e-05</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.487851245154161e-06</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3.471303352853283e-05</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.0001298848656006157</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>5.776000034529716e-05</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.659405072336085e-05</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.0002163256285712123</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>5.77788978262106e-06</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.385356699756812e-05</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>4.43754925072426e-06</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>6.111074617365375e-05</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.641954233695287e-05</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>9.90480839391239e-06</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.928680598619394e-07</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3.425406612223014e-05</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.0001705136382952332</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.108737655566074e-05</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.173333218204789e-05</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.0002861501707229763</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.995424620166887e-05</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.033675446000416e-05</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.0001018416660372168</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.0002971842186525464</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.066025470208842e-05</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.973833761643618e-05</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.751724191009998e-05</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.256871994177345e-05</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.644051710376516e-05</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.05252220237162e-05</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.049904989893548e-05</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4.168156738160178e-05</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.496092904242687e-05</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>7.711397302045953e-06</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.0001180163817480206</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.597113805473782e-05</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>5.181390588404611e-05</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>8.427737338934094e-05</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>2.010057414736366e-06</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.69455992768053e-05</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>6.722272519255057e-05</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>2.616727215354331e-05</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>7.573748735012487e-05</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>8.849199366522953e-05</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>4.922847438137978e-05</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>8.303184586111456e-06</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.0001450542767997831</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>6.003208545735106e-05</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>6.870309880468994e-05</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>2.543053051340394e-05</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0.0001228814071509987</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>6.743215635651723e-06</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>6.371517520165071e-05</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>9.47619992075488e-06</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>1.74741362570785e-05</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>7.434622966684401e-05</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>2.582231718406547e-05</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>1.259935470443452e-05</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>6.546779331983998e-06</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>9.878553100861609e-05</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>4.539005749393255e-05</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>1.003595207293984e-05</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>1.28990850498667e-05</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>4.123991675442085e-05</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0.0001562044199090451</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>9.363506978843361e-05</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>3.846585605060682e-05</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>3.190243660355918e-05</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>5.564518505707383e-05</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>1.694131969998125e-05</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>5.110041092848405e-05</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>1.670693200139794e-05</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>8.452307156403549e-06</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>7.369132799794897e-05</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>1.72023537743371e-05</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>2.707717430894263e-05</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>1.286040969716851e-05</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0.0001045215904014185</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>1.933579551405273e-05</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>2.577407576609403e-05</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>2.43954536927049e-06</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>7.985367119545117e-06</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>1.522362163086655e-05</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>6.978082092246041e-05</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>4.575779166771099e-05</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.0001315558038186282</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>4.319319941714639e-06</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>6.548521196236834e-05</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>2.930799382738769e-05</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>2.057236997643486e-05</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>2.553167905716691e-05</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>4.290702418074943e-05</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>2.544091148592997e-05</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>7.829566311556846e-05</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>2.243138396806899e-06</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>1.736205922497902e-05</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>2.098995537380688e-05</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0.0001354407868348062</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>1.025127949105809e-05</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>2.333257361897267e-05</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>1.186498866445618e-05</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>5.290157787385397e-05</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>1.163794513558969e-05</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>3.257242133258842e-05</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>6.919238512637094e-05</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>3.209810529369861e-05</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>3.017358176293783e-05</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0.0001038287300616503</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>3.433970778132789e-05</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>1.388274995406391e-05</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>2.392409260210115e-05</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>2.119037162628956e-05</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>3.362865390954539e-05</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>8.755896851653233e-05</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>4.594742131303065e-05</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>5.327000326360576e-05</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>1.109224831452593e-05</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>8.377332051168196e-06</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>2.482901982148178e-05</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>5.808829882880673e-05</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>6.472452514572069e-05</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>9.560276339470875e-06</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>3.483943510218523e-05</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>6.749968633812387e-06</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>9.102413969230838e-06</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>3.548630775185302e-05</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>1.140065614890773e-05</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>9.037541894940659e-05</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>2.649519228725694e-05</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>1.819779572542757e-05</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>2.25729017984122e-05</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>8.786426769802347e-05</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>4.110354348085821e-05</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>1.744762448652182e-05</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>1.233020702784415e-05</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>2.933198175014695e-06</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0.0001019643459585495</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>7.293162343557924e-05</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>5.755294841947034e-05</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>7.311893568839878e-06</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>8.808277925709262e-05</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>3.823284350801259e-05</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0.0001063941963366233</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>5.184318069950677e-05</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>3.009982538060285e-05</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>1.948363387782592e-05</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0.0001308589417021722</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>4.136702773394063e-05</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>2.114220478688367e-06</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>4.477769834920764e-07</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>7.344759796978906e-05</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>9.390522609464824e-05</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0.0001173750788439065</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>5.245282591204159e-05</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>6.943754851818085e-05</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>5.343599332263693e-05</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>3.103372819168726e-06</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0.0001504041283624247</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>8.719952165847644e-05</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>1.053596861311235e-06</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>1.14865651994478e-05</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>6.558116729138419e-05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2.738136606339481e-09</v>
+      </c>
+      <c r="B16" t="n">
+        <v>7.044560490498952e-09</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5.378338885364542e-10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.569346957415064e-09</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.961948242230505e-09</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.983173181230313e-09</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.511969993650553e-09</v>
+      </c>
+      <c r="H16" t="n">
+        <v>9.323758431989404e-10</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.705369956361835e-09</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.921677675464366e-10</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8.729823086639499e-09</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4.366734474015033e-10</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.51374093657364e-09</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.02779684552479e-09</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.668806648424948e-09</v>
+      </c>
+      <c r="P16" t="n">
+        <v>9.926884869670971e-10</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.78105516393623e-09</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.284208822089795e-09</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.766404522651754e-10</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.305439312204726e-09</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7.583612626760328e-10</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.200258448186275e-09</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.982552733093002e-10</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.542897004076394e-10</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.011030897364208e-09</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.238671387682189e-09</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>7.041465188706297e-10</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>9.932015210267764e-10</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.460831007501724e-10</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.261483305649904e-10</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.287535272316177e-09</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.484518368817135e-09</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.621834222476082e-09</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>3.674995030511496e-10</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>3.347535582065575e-09</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.205504918111444e-09</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>8.589342570530789e-10</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.4657149938202e-09</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>4.149356414018257e-10</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.793003634453783e-09</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>5.268323555185361e-10</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>6.244493810925178e-10</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.066296162477443e-09</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.13341802610023e-09</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.288615573777577e-10</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.63250271476312e-12</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.546439111967175e-09</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>7.151924608095328e-10</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.205657878562306e-09</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>2.630924367252874e-09</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>2.242870777990902e-09</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>2.517779040811519e-10</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.502568847122632e-09</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.446050390541131e-09</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>6.824675269356817e-10</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>2.607719040703671e-10</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>2.880418126238737e-11</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3.30176019858186e-09</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>6.172393152148459e-11</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>4.425382837958125e-10</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>5.510506495554068e-10</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>1.890670731086175e-09</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>7.545197799885273e-11</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>4.905414963118915e-10</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.341633582008228e-09</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5.337706387997798e-10</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.889750356198761e-09</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>2.891543671168506e-09</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>4.026637356879803e-10</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1.406287530869577e-09</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>9.955568591735187e-10</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>2.381009001073409e-10</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>7.156424342014134e-10</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>5.821984672138569e-09</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>6.579989886290605e-10</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>3.186030606006085e-11</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>1.057515408575682e-09</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>8.810000506898064e-10</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>1.740412036710381e-09</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>5.05327613087303e-10</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>5.147887671697049e-10</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>6.542263397690817e-10</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>2.259771481050166e-09</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>2.877072746709786e-10</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>5.574713468625703e-10</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>7.208542651682137e-10</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>5.733123975559806e-10</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>5.307514983066142e-10</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>2.627444373182186e-10</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>1.780288971797717e-10</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>2.555731626330271e-09</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>5.480047526873477e-09</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>5.879411402176515e-10</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>6.971567212410434e-10</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>1.129920823572661e-09</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>6.872694080506392e-10</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>2.774602547717109e-09</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>2.353394701337663e-10</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>2.4811264154323e-10</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>2.220078287873406e-10</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>2.143615951410993e-09</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>1.591929504884959e-10</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>9.559522062829728e-10</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>6.813682396078491e-10</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>9.161393865753098e-10</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>9.131780887017271e-10</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>5.043035433693888e-12</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>3.617392496657601e-10</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>1.301662444497254e-09</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>1.278513739322307e-09</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>9.868823536152149e-10</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>1.491621937077525e-09</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>2.995571124486673e-09</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>1.428396068092752e-09</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>2.082432837280379e-11</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>1.381973202541076e-09</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>1.297347340667443e-09</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>4.624134963826521e-10</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>1.157362317094623e-09</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>2.568351087361975e-10</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>2.173024815643743e-10</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>3.771648271477801e-10</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>7.034766102975709e-10</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>8.316076716141652e-10</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>1.904350455106396e-09</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>4.406319753513799e-10</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>5.938415315043244e-10</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>1.543664862602157e-09</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>7.910881671957526e-11</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>1.032968932612732e-09</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>5.019879512069281e-10</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>8.47681924653898e-10</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>6.736917690375321e-10</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>1.869442822766132e-09</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>2.261886788978984e-10</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>1.471895050286776e-09</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>8.402900042447925e-10</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>4.866568814598793e-10</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>1.454746878515323e-10</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>1.462100218674323e-09</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>3.016264182864603e-10</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>6.374126226837973e-10</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>5.069156205905756e-10</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>3.554946059747266e-10</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>4.495321892505899e-10</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>4.029215849854495e-10</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>4.446230050803024e-10</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>7.417437775103508e-10</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>1.851000130947966e-09</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>3.743186316462754e-12</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>1.7139454785986e-11</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>1.007703809285942e-09</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>1.689879070010392e-10</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>6.087128578968759e-10</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>2.644194196932403e-09</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>1.288211481931256e-10</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>8.539975948629319e-10</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>4.743729298262167e-10</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>7.561192227889535e-10</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>3.450494334700238e-10</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>3.353979871612012e-10</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>3.686997374074963e-10</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>1.093200308055486e-09</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>1.073558131281516e-09</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>3.86255610829167e-10</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>8.022097430782082e-10</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>9.943810219681382e-10</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>1.123779735934249e-09</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>4.390711960677862e-10</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>1.162143714594777e-10</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>2.528441900295775e-10</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>1.692394113739226e-09</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>2.730115022941959e-10</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>4.588197599630917e-10</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>2.849024793860622e-09</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>2.319101799486134e-09</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>9.126386313340618e-10</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>2.127192866296923e-09</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>5.682188053413029e-11</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>1.086380652104424e-09</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>4.177858059506434e-10</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>1.42190104135409e-09</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>8.288001396294931e-10</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>2.004440224911974e-10</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>1.222575596315778e-09</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>2.465466053536147e-09</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>1.564133378373356e-09</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>1.258954385185973e-09</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>1.426198048548599e-10</v>
       </c>
     </row>
   </sheetData>
